--- a/DATOS/Datos crudos/Históricos Presupuesto.xlsx
+++ b/DATOS/Datos crudos/Históricos Presupuesto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5fa8a9efe53b17c/Documentos/TP FINAL DATOS/DATOS/Datos crudos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_CB058261CB385EDFDA183B0CA1E891AFD703258D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{239AD1A7-6DE3-4160-B195-5197BD21F9ED}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_CB058261CB385EDFDA183B0CA1E891AFD703258D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46006D8D-83E9-460C-BC3E-BEB20C4179C3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10374" uniqueCount="2251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10354" uniqueCount="2235">
   <si>
     <t>Año</t>
   </si>
@@ -6679,84 +6679,42 @@
     <t>Iluminación del Playón de la Estación Villa Adelina</t>
   </si>
   <si>
-    <t>82.455,00</t>
-  </si>
-  <si>
     <t>Plaza Libertad</t>
   </si>
   <si>
     <t>Puesta en valor de la Plaza</t>
   </si>
   <si>
-    <t>430.000,00</t>
-  </si>
-  <si>
-    <t>109.538,00</t>
-  </si>
-  <si>
     <t>Iluminación del perímetro de la Plaza</t>
   </si>
   <si>
-    <t>31.630,00</t>
-  </si>
-  <si>
     <t>Plaza Octavio Ortiz</t>
   </si>
   <si>
     <t>Iluminación de la Plaza</t>
   </si>
   <si>
-    <t>68.480,00</t>
-  </si>
-  <si>
-    <t>38.217,00</t>
-  </si>
-  <si>
     <t>Reparación de veredas rotas por raíces de árboles</t>
   </si>
   <si>
-    <t>577.978,00</t>
-  </si>
-  <si>
     <t>Poda, limpieza en general y mejoramiento de iluminación</t>
   </si>
   <si>
-    <t>55.584,00</t>
-  </si>
-  <si>
-    <t>188.148,00</t>
-  </si>
-  <si>
     <t>Plaza de los Inmigrantes</t>
   </si>
   <si>
     <t>Mejoramiento de iluminación de la Plaza</t>
   </si>
   <si>
-    <t>61.595,00</t>
-  </si>
-  <si>
-    <t>98.310,00</t>
-  </si>
-  <si>
     <t>Plaza "Vicente López y Planes"</t>
   </si>
   <si>
     <t>Mejoramiento de iluminación en la Plaza</t>
   </si>
   <si>
-    <t>35.088,00</t>
-  </si>
-  <si>
-    <t>486.200,00</t>
-  </si>
-  <si>
     <t>Instalación de reducidores de velocidad en túneles</t>
   </si>
   <si>
-    <t>14.164,00</t>
-  </si>
-  <si>
     <t>Compra e instalación de 2 cámaras de seguridad fijas</t>
   </si>
   <si>
@@ -6766,13 +6724,7 @@
     <t>PISTA BMX etapa 1 (movimiento de suelos)</t>
   </si>
   <si>
-    <t>147.000,00</t>
-  </si>
-  <si>
     <t>PISTA BMX etapa 2 (partidor)</t>
-  </si>
-  <si>
-    <t>550.000,00</t>
   </si>
 </sst>
 </file>
@@ -6808,8 +6760,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7151,9 +7105,11 @@
   <dimension ref="A1:M798"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="5" max="5" width="38.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="53.109375" customWidth="1"/>
     <col min="7" max="7" width="12.5546875" customWidth="1"/>
     <col min="11" max="11" width="37" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -7169,7 +7125,7 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -7210,7 +7166,7 @@
       <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F2" t="s">
@@ -7251,7 +7207,7 @@
       <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F3" t="s">
@@ -7292,7 +7248,7 @@
       <c r="D4" t="s">
         <v>36</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F4" t="s">
@@ -7333,7 +7289,7 @@
       <c r="D5" t="s">
         <v>44</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F5" t="s">
@@ -7374,7 +7330,7 @@
       <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F6" t="s">
@@ -7415,7 +7371,7 @@
       <c r="D7" t="s">
         <v>56</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F7" t="s">
@@ -7456,7 +7412,7 @@
       <c r="D8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F8" t="s">
@@ -7497,7 +7453,7 @@
       <c r="D9" t="s">
         <v>65</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>66</v>
       </c>
       <c r="F9" t="s">
@@ -7538,7 +7494,7 @@
       <c r="D10" t="s">
         <v>72</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>73</v>
       </c>
       <c r="F10" t="s">
@@ -7579,7 +7535,7 @@
       <c r="D11" t="s">
         <v>76</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F11" t="s">
@@ -7620,7 +7576,7 @@
       <c r="D12" t="s">
         <v>80</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F12" t="s">
@@ -7661,7 +7617,7 @@
       <c r="D13" t="s">
         <v>83</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>84</v>
       </c>
       <c r="F13" t="s">
@@ -7702,7 +7658,7 @@
       <c r="D14" t="s">
         <v>87</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>88</v>
       </c>
       <c r="F14" t="s">
@@ -7743,7 +7699,7 @@
       <c r="D15" t="s">
         <v>91</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>92</v>
       </c>
       <c r="F15" t="s">
@@ -7784,7 +7740,7 @@
       <c r="D16" t="s">
         <v>95</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>96</v>
       </c>
       <c r="F16" t="s">
@@ -7825,7 +7781,7 @@
       <c r="D17" t="s">
         <v>100</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>101</v>
       </c>
       <c r="F17" t="s">
@@ -7866,7 +7822,7 @@
       <c r="D18" t="s">
         <v>105</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F18" t="s">
@@ -7907,7 +7863,7 @@
       <c r="D19" t="s">
         <v>109</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F19" t="s">
@@ -7948,7 +7904,7 @@
       <c r="D20" t="s">
         <v>113</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F20" t="s">
@@ -7989,7 +7945,7 @@
       <c r="D21" t="s">
         <v>117</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F21" t="s">
@@ -8030,7 +7986,7 @@
       <c r="D22" t="s">
         <v>120</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F22" t="s">
@@ -8071,7 +8027,7 @@
       <c r="D23" t="s">
         <v>123</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F23" t="s">
@@ -8112,7 +8068,7 @@
       <c r="D24" t="s">
         <v>128</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>129</v>
       </c>
       <c r="F24" t="s">
@@ -8153,7 +8109,7 @@
       <c r="D25" t="s">
         <v>134</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F25" t="s">
@@ -8194,7 +8150,7 @@
       <c r="D26" t="s">
         <v>139</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1" t="s">
         <v>88</v>
       </c>
       <c r="F26" t="s">
@@ -8235,7 +8191,7 @@
       <c r="D27" t="s">
         <v>144</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F27" t="s">
@@ -8276,7 +8232,7 @@
       <c r="D28" t="s">
         <v>146</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F28" t="s">
@@ -8317,7 +8273,7 @@
       <c r="D29" t="s">
         <v>149</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1" t="s">
         <v>150</v>
       </c>
       <c r="F29" t="s">
@@ -8358,7 +8314,7 @@
       <c r="D30" t="s">
         <v>155</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F30" t="s">
@@ -8399,7 +8355,7 @@
       <c r="D31" t="s">
         <v>159</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1" t="s">
         <v>160</v>
       </c>
       <c r="F31" t="s">
@@ -8440,7 +8396,7 @@
       <c r="D32" t="s">
         <v>163</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>164</v>
       </c>
       <c r="F32" t="s">
@@ -8481,7 +8437,7 @@
       <c r="D33" t="s">
         <v>168</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F33" t="s">
@@ -8522,7 +8478,7 @@
       <c r="D34" t="s">
         <v>171</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1" t="s">
         <v>172</v>
       </c>
       <c r="F34" t="s">
@@ -8563,7 +8519,7 @@
       <c r="D35" t="s">
         <v>175</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1" t="s">
         <v>176</v>
       </c>
       <c r="F35" t="s">
@@ -8604,7 +8560,7 @@
       <c r="D36" t="s">
         <v>178</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F36" t="s">
@@ -8645,7 +8601,7 @@
       <c r="D37" t="s">
         <v>182</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1" t="s">
         <v>183</v>
       </c>
       <c r="F37" t="s">
@@ -8686,7 +8642,7 @@
       <c r="D38" t="s">
         <v>186</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F38" t="s">
@@ -8727,7 +8683,7 @@
       <c r="D39" t="s">
         <v>189</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F39" t="s">
@@ -8768,7 +8724,7 @@
       <c r="D40" t="s">
         <v>192</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F40" t="s">
@@ -8809,7 +8765,7 @@
       <c r="D41" t="s">
         <v>195</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F41" t="s">
@@ -8850,7 +8806,7 @@
       <c r="D42" t="s">
         <v>199</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F42" t="s">
@@ -8891,7 +8847,7 @@
       <c r="D43" t="s">
         <v>203</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1" t="s">
         <v>204</v>
       </c>
       <c r="F43" t="s">
@@ -8932,7 +8888,7 @@
       <c r="D44" t="s">
         <v>207</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1" t="s">
         <v>208</v>
       </c>
       <c r="F44" t="s">
@@ -8973,7 +8929,7 @@
       <c r="D45" t="s">
         <v>211</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>212</v>
       </c>
       <c r="F45" t="s">
@@ -9014,7 +8970,7 @@
       <c r="D46" t="s">
         <v>216</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F46" t="s">
@@ -9055,7 +9011,7 @@
       <c r="D47" t="s">
         <v>220</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F47" t="s">
@@ -9096,7 +9052,7 @@
       <c r="D48" t="s">
         <v>224</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F48" t="s">
@@ -9137,7 +9093,7 @@
       <c r="D49" t="s">
         <v>227</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>228</v>
       </c>
       <c r="F49" t="s">
@@ -9178,7 +9134,7 @@
       <c r="D50" t="s">
         <v>230</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F50" t="s">
@@ -9219,7 +9175,7 @@
       <c r="D51" t="s">
         <v>232</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F51" t="s">
@@ -9260,7 +9216,7 @@
       <c r="D52" t="s">
         <v>236</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F52" t="s">
@@ -9301,7 +9257,7 @@
       <c r="D53" t="s">
         <v>239</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F53" t="s">
@@ -9342,7 +9298,7 @@
       <c r="D54" t="s">
         <v>189</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F54" t="s">
@@ -9383,7 +9339,7 @@
       <c r="D55" t="s">
         <v>243</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F55" t="s">
@@ -9424,7 +9380,7 @@
       <c r="D56" t="s">
         <v>247</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F56" t="s">
@@ -9465,7 +9421,7 @@
       <c r="D57" t="s">
         <v>250</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57" s="1" t="s">
         <v>251</v>
       </c>
       <c r="F57" t="s">
@@ -9506,7 +9462,7 @@
       <c r="D58" t="s">
         <v>254</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F58" t="s">
@@ -9547,7 +9503,7 @@
       <c r="D59" t="s">
         <v>257</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="1" t="s">
         <v>258</v>
       </c>
       <c r="F59" t="s">
@@ -9588,7 +9544,7 @@
       <c r="D60" t="s">
         <v>261</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F60" t="s">
@@ -9629,7 +9585,7 @@
       <c r="D61" t="s">
         <v>264</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="1" t="s">
         <v>265</v>
       </c>
       <c r="F61" t="s">
@@ -9670,7 +9626,7 @@
       <c r="D62" t="s">
         <v>268</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="1" t="s">
         <v>269</v>
       </c>
       <c r="F62" t="s">
@@ -9711,7 +9667,7 @@
       <c r="D63" t="s">
         <v>273</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="1" t="s">
         <v>274</v>
       </c>
       <c r="F63" t="s">
@@ -9752,7 +9708,7 @@
       <c r="D64" t="s">
         <v>149</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="1" t="s">
         <v>276</v>
       </c>
       <c r="F64" t="s">
@@ -9793,7 +9749,7 @@
       <c r="D65" t="s">
         <v>280</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" s="1" t="s">
         <v>281</v>
       </c>
       <c r="F65" t="s">
@@ -9834,7 +9790,7 @@
       <c r="D66" t="s">
         <v>284</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="1" t="s">
         <v>285</v>
       </c>
       <c r="F66" t="s">
@@ -9875,7 +9831,7 @@
       <c r="D67" t="s">
         <v>288</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F67" t="s">
@@ -9916,7 +9872,7 @@
       <c r="D68" t="s">
         <v>292</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="1" t="s">
         <v>293</v>
       </c>
       <c r="F68" t="s">
@@ -9957,7 +9913,7 @@
       <c r="D69" t="s">
         <v>298</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="1" t="s">
         <v>299</v>
       </c>
       <c r="F69" t="s">
@@ -9998,7 +9954,7 @@
       <c r="D70" t="s">
         <v>302</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F70" t="s">
@@ -10039,7 +9995,7 @@
       <c r="D71" t="s">
         <v>305</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F71" t="s">
@@ -10080,7 +10036,7 @@
       <c r="D72" t="s">
         <v>308</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F72" t="s">
@@ -10121,7 +10077,7 @@
       <c r="D73" t="s">
         <v>302</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F73" t="s">
@@ -10162,7 +10118,7 @@
       <c r="D74" t="s">
         <v>314</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F74" t="s">
@@ -10203,7 +10159,7 @@
       <c r="D75" t="s">
         <v>317</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F75" t="s">
@@ -10244,7 +10200,7 @@
       <c r="D76" t="s">
         <v>320</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" s="1" t="s">
         <v>129</v>
       </c>
       <c r="F76" t="s">
@@ -10285,7 +10241,7 @@
       <c r="D77" t="s">
         <v>324</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F77" t="s">
@@ -10326,7 +10282,7 @@
       <c r="D78" t="s">
         <v>329</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F78" t="s">
@@ -10367,7 +10323,7 @@
       <c r="D79" t="s">
         <v>332</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F79" t="s">
@@ -10408,7 +10364,7 @@
       <c r="D80" t="s">
         <v>335</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="1" t="s">
         <v>336</v>
       </c>
       <c r="F80" t="s">
@@ -10449,7 +10405,7 @@
       <c r="D81" t="s">
         <v>339</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F81" t="s">
@@ -10490,7 +10446,7 @@
       <c r="D82" t="s">
         <v>342</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F82" t="s">
@@ -10531,7 +10487,7 @@
       <c r="D83" t="s">
         <v>344</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="1" t="s">
         <v>293</v>
       </c>
       <c r="F83" t="s">
@@ -10572,7 +10528,7 @@
       <c r="D84" t="s">
         <v>347</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="1" t="s">
         <v>348</v>
       </c>
       <c r="F84" t="s">
@@ -10613,7 +10569,7 @@
       <c r="D85" t="s">
         <v>350</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F85" t="s">
@@ -10654,7 +10610,7 @@
       <c r="D86" t="s">
         <v>352</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F86" t="s">
@@ -10695,7 +10651,7 @@
       <c r="D87" t="s">
         <v>355</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="1" t="s">
         <v>356</v>
       </c>
       <c r="F87" t="s">
@@ -10736,7 +10692,7 @@
       <c r="D88" t="s">
         <v>360</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="1" t="s">
         <v>285</v>
       </c>
       <c r="F88" t="s">
@@ -10777,7 +10733,7 @@
       <c r="D89" t="s">
         <v>363</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F89" t="s">
@@ -10818,7 +10774,7 @@
       <c r="D90" t="s">
         <v>367</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="1" t="s">
         <v>368</v>
       </c>
       <c r="F90" t="s">
@@ -10859,7 +10815,7 @@
       <c r="D91" t="s">
         <v>371</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F91" t="s">
@@ -10900,7 +10856,7 @@
       <c r="D92" t="s">
         <v>344</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="1" t="s">
         <v>293</v>
       </c>
       <c r="F92" t="s">
@@ -10941,7 +10897,7 @@
       <c r="D93" t="s">
         <v>377</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F93" t="s">
@@ -10982,7 +10938,7 @@
       <c r="D94" t="s">
         <v>380</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="1" t="s">
         <v>381</v>
       </c>
       <c r="F94" t="s">
@@ -11023,7 +10979,7 @@
       <c r="D95" t="s">
         <v>384</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F95" t="s">
@@ -11064,7 +11020,7 @@
       <c r="D96" t="s">
         <v>387</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="1" t="s">
         <v>258</v>
       </c>
       <c r="F96" t="s">
@@ -11105,7 +11061,7 @@
       <c r="D97" t="s">
         <v>302</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F97" t="s">
@@ -11146,7 +11102,7 @@
       <c r="D98" t="s">
         <v>392</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="1" t="s">
         <v>393</v>
       </c>
       <c r="F98" t="s">
@@ -11187,7 +11143,7 @@
       <c r="D99" t="s">
         <v>280</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="1" t="s">
         <v>396</v>
       </c>
       <c r="F99" t="s">
@@ -11228,7 +11184,7 @@
       <c r="D100" t="s">
         <v>302</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F100" t="s">
@@ -11269,7 +11225,7 @@
       <c r="D101" t="s">
         <v>401</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F101" t="s">
@@ -11310,7 +11266,7 @@
       <c r="D102" t="s">
         <v>308</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="1" t="s">
         <v>403</v>
       </c>
       <c r="F102" t="s">
@@ -11351,7 +11307,7 @@
       <c r="D103" t="s">
         <v>406</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F103" t="s">
@@ -11392,7 +11348,7 @@
       <c r="D104" t="s">
         <v>302</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F104" t="s">
@@ -11433,7 +11389,7 @@
       <c r="D105" t="s">
         <v>344</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="1" t="s">
         <v>293</v>
       </c>
       <c r="F105" t="s">
@@ -11474,7 +11430,7 @@
       <c r="D106" t="s">
         <v>412</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F106" t="s">
@@ -11515,7 +11471,7 @@
       <c r="D107" t="s">
         <v>302</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F107" t="s">
@@ -11556,7 +11512,7 @@
       <c r="D108" t="s">
         <v>302</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F108" t="s">
@@ -11597,7 +11553,7 @@
       <c r="D109" t="s">
         <v>418</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F109" t="s">
@@ -11638,7 +11594,7 @@
       <c r="D110" t="s">
         <v>420</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="1" t="s">
         <v>421</v>
       </c>
       <c r="F110" t="s">
@@ -11679,7 +11635,7 @@
       <c r="D111" t="s">
         <v>302</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="1" t="s">
         <v>424</v>
       </c>
       <c r="F111" t="s">
@@ -11720,7 +11676,7 @@
       <c r="D112" t="s">
         <v>344</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="1" t="s">
         <v>293</v>
       </c>
       <c r="F112" t="s">
@@ -11761,7 +11717,7 @@
       <c r="D113" t="s">
         <v>308</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="1" t="s">
         <v>403</v>
       </c>
       <c r="F113" t="s">
@@ -11802,7 +11758,7 @@
       <c r="D114" t="s">
         <v>302</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F114" t="s">
@@ -11843,7 +11799,7 @@
       <c r="D115" t="s">
         <v>432</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="1" t="s">
         <v>433</v>
       </c>
       <c r="F115" t="s">
@@ -11884,7 +11840,7 @@
       <c r="D116" t="s">
         <v>437</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="1" t="s">
         <v>438</v>
       </c>
       <c r="F116" t="s">
@@ -11925,7 +11881,7 @@
       <c r="D117" t="s">
         <v>440</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="1" t="s">
         <v>441</v>
       </c>
       <c r="F117" t="s">
@@ -11966,7 +11922,7 @@
       <c r="D118" t="s">
         <v>444</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="1" t="s">
         <v>445</v>
       </c>
       <c r="F118" t="s">
@@ -12007,7 +11963,7 @@
       <c r="D119" t="s">
         <v>344</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F119" t="s">
@@ -12048,7 +12004,7 @@
       <c r="D120" t="s">
         <v>449</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F120" t="s">
@@ -12089,7 +12045,7 @@
       <c r="D121" t="s">
         <v>452</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" s="1" t="s">
         <v>453</v>
       </c>
       <c r="F121" t="s">
@@ -12130,7 +12086,7 @@
       <c r="D122" t="s">
         <v>456</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" s="1" t="s">
         <v>457</v>
       </c>
       <c r="F122" t="s">
@@ -12171,7 +12127,7 @@
       <c r="D123" t="s">
         <v>460</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" s="1" t="s">
         <v>285</v>
       </c>
       <c r="F123" t="s">
@@ -12212,7 +12168,7 @@
       <c r="D124" t="s">
         <v>302</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F124" t="s">
@@ -12253,7 +12209,7 @@
       <c r="D125" t="s">
         <v>449</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F125" t="s">
@@ -12294,7 +12250,7 @@
       <c r="D126" t="s">
         <v>302</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F126" t="s">
@@ -12335,7 +12291,7 @@
       <c r="D127" t="s">
         <v>302</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F127" t="s">
@@ -12376,7 +12332,7 @@
       <c r="D128" t="s">
         <v>471</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="1" t="s">
         <v>472</v>
       </c>
       <c r="F128" t="s">
@@ -12417,7 +12373,7 @@
       <c r="D129" t="s">
         <v>474</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" s="1" t="s">
         <v>285</v>
       </c>
       <c r="F129" t="s">
@@ -12458,7 +12414,7 @@
       <c r="D130" t="s">
         <v>477</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="1" t="s">
         <v>478</v>
       </c>
       <c r="F130" t="s">
@@ -12499,7 +12455,7 @@
       <c r="D131" t="s">
         <v>302</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F131" t="s">
@@ -12540,7 +12496,7 @@
       <c r="D132" t="s">
         <v>481</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="1" t="s">
         <v>482</v>
       </c>
       <c r="F132" t="s">
@@ -12581,7 +12537,7 @@
       <c r="D133" t="s">
         <v>302</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="1" t="s">
         <v>289</v>
       </c>
       <c r="F133" t="s">
@@ -12622,7 +12578,7 @@
       <c r="D134" t="s">
         <v>488</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F134" t="s">
@@ -12663,7 +12619,7 @@
       <c r="D135" t="s">
         <v>490</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F135" t="s">
@@ -12704,7 +12660,7 @@
       <c r="D136" t="s">
         <v>493</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F136" t="s">
@@ -12745,7 +12701,7 @@
       <c r="D137" t="s">
         <v>496</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="1" t="s">
         <v>497</v>
       </c>
       <c r="F137" t="s">
@@ -12786,7 +12742,7 @@
       <c r="D138" t="s">
         <v>500</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F138" t="s">
@@ -12827,7 +12783,7 @@
       <c r="D139" t="s">
         <v>503</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="1" t="s">
         <v>504</v>
       </c>
       <c r="F139" t="s">
@@ -12868,7 +12824,7 @@
       <c r="D140" t="s">
         <v>507</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F140" t="s">
@@ -12909,7 +12865,7 @@
       <c r="D141" t="s">
         <v>510</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E141" s="1" t="s">
         <v>511</v>
       </c>
       <c r="F141" t="s">
@@ -12950,7 +12906,7 @@
       <c r="D142" t="s">
         <v>514</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E142" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F142" t="s">
@@ -12991,7 +12947,7 @@
       <c r="D143" t="s">
         <v>517</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E143" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F143" t="s">
@@ -13032,7 +12988,7 @@
       <c r="D144" t="s">
         <v>493</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F144" t="s">
@@ -13073,7 +13029,7 @@
       <c r="D145" t="s">
         <v>520</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E145" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F145" t="s">
@@ -13114,7 +13070,7 @@
       <c r="D146" t="s">
         <v>523</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E146" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F146" t="s">
@@ -13155,7 +13111,7 @@
       <c r="D147" t="s">
         <v>526</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E147" s="1" t="s">
         <v>527</v>
       </c>
       <c r="F147" t="s">
@@ -13196,7 +13152,7 @@
       <c r="D148" t="s">
         <v>530</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E148" s="1" t="s">
         <v>531</v>
       </c>
       <c r="F148" t="s">
@@ -13237,7 +13193,7 @@
       <c r="D149" t="s">
         <v>534</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E149" s="1" t="s">
         <v>535</v>
       </c>
       <c r="F149" t="s">
@@ -13278,7 +13234,7 @@
       <c r="D150" t="s">
         <v>493</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E150" s="1" t="s">
         <v>537</v>
       </c>
       <c r="F150" t="s">
@@ -13319,7 +13275,7 @@
       <c r="D151" t="s">
         <v>539</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E151" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F151" t="s">
@@ -13360,7 +13316,7 @@
       <c r="D152" t="s">
         <v>542</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E152" s="1" t="s">
         <v>543</v>
       </c>
       <c r="F152" t="s">
@@ -13401,7 +13357,7 @@
       <c r="D153" t="s">
         <v>546</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E153" s="1" t="s">
         <v>547</v>
       </c>
       <c r="F153" t="s">
@@ -13442,7 +13398,7 @@
       <c r="D154" t="s">
         <v>549</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E154" s="1" t="s">
         <v>550</v>
       </c>
       <c r="F154" t="s">
@@ -13483,7 +13439,7 @@
       <c r="D155" t="s">
         <v>553</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E155" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F155" t="s">
@@ -13524,7 +13480,7 @@
       <c r="D156" t="s">
         <v>555</v>
       </c>
-      <c r="E156" t="s">
+      <c r="E156" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F156" t="s">
@@ -13565,7 +13521,7 @@
       <c r="D157" t="s">
         <v>556</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E157" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F157" t="s">
@@ -13606,7 +13562,7 @@
       <c r="D158" t="s">
         <v>558</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E158" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F158" t="s">
@@ -13647,7 +13603,7 @@
       <c r="D159" t="s">
         <v>560</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E159" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F159" t="s">
@@ -13688,7 +13644,7 @@
       <c r="D160" t="s">
         <v>493</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E160" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F160" t="s">
@@ -13729,7 +13685,7 @@
       <c r="D161" t="s">
         <v>564</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E161" s="1" t="s">
         <v>565</v>
       </c>
       <c r="F161" t="s">
@@ -13770,7 +13726,7 @@
       <c r="D162" t="s">
         <v>567</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E162" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F162" t="s">
@@ -13811,7 +13767,7 @@
       <c r="D163" t="s">
         <v>570</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E163" s="1" t="s">
         <v>571</v>
       </c>
       <c r="F163" t="s">
@@ -13852,7 +13808,7 @@
       <c r="D164" t="s">
         <v>573</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E164" s="1" t="s">
         <v>574</v>
       </c>
       <c r="F164" t="s">
@@ -13893,7 +13849,7 @@
       <c r="D165" t="s">
         <v>576</v>
       </c>
-      <c r="E165" t="s">
+      <c r="E165" s="1" t="s">
         <v>577</v>
       </c>
       <c r="F165" t="s">
@@ -13934,7 +13890,7 @@
       <c r="D166" t="s">
         <v>580</v>
       </c>
-      <c r="E166" t="s">
+      <c r="E166" s="1" t="s">
         <v>581</v>
       </c>
       <c r="F166" t="s">
@@ -13975,7 +13931,7 @@
       <c r="D167" t="s">
         <v>584</v>
       </c>
-      <c r="E167" t="s">
+      <c r="E167" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F167" t="s">
@@ -14016,7 +13972,7 @@
       <c r="D168" t="s">
         <v>587</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E168" s="1" t="s">
         <v>588</v>
       </c>
       <c r="F168" t="s">
@@ -14057,7 +14013,7 @@
       <c r="D169" t="s">
         <v>591</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E169" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F169" t="s">
@@ -14098,7 +14054,7 @@
       <c r="D170" t="s">
         <v>493</v>
       </c>
-      <c r="E170" t="s">
+      <c r="E170" s="1" t="s">
         <v>537</v>
       </c>
       <c r="F170" t="s">
@@ -14139,7 +14095,7 @@
       <c r="D171" t="s">
         <v>594</v>
       </c>
-      <c r="E171" t="s">
+      <c r="E171" s="1" t="s">
         <v>595</v>
       </c>
       <c r="F171" t="s">
@@ -14180,7 +14136,7 @@
       <c r="D172" t="s">
         <v>598</v>
       </c>
-      <c r="E172" t="s">
+      <c r="E172" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F172" t="s">
@@ -14221,7 +14177,7 @@
       <c r="D173" t="s">
         <v>493</v>
       </c>
-      <c r="E173" t="s">
+      <c r="E173" s="1" t="s">
         <v>537</v>
       </c>
       <c r="F173" t="s">
@@ -14262,7 +14218,7 @@
       <c r="D174" t="s">
         <v>602</v>
       </c>
-      <c r="E174" t="s">
+      <c r="E174" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F174" t="s">
@@ -14303,7 +14259,7 @@
       <c r="D175" t="s">
         <v>605</v>
       </c>
-      <c r="E175" t="s">
+      <c r="E175" s="1" t="s">
         <v>606</v>
       </c>
       <c r="F175" t="s">
@@ -14344,7 +14300,7 @@
       <c r="D176" t="s">
         <v>549</v>
       </c>
-      <c r="E176" t="s">
+      <c r="E176" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F176" t="s">
@@ -14385,7 +14341,7 @@
       <c r="D177" t="s">
         <v>609</v>
       </c>
-      <c r="E177" t="s">
+      <c r="E177" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F177" t="s">
@@ -14426,7 +14382,7 @@
       <c r="D178" t="s">
         <v>611</v>
       </c>
-      <c r="E178" t="s">
+      <c r="E178" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F178" t="s">
@@ -14467,7 +14423,7 @@
       <c r="D179" t="s">
         <v>612</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E179" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F179" t="s">
@@ -14508,7 +14464,7 @@
       <c r="D180" t="s">
         <v>615</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E180" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F180" t="s">
@@ -14549,7 +14505,7 @@
       <c r="D181" t="s">
         <v>618</v>
       </c>
-      <c r="E181" t="s">
+      <c r="E181" s="1" t="s">
         <v>619</v>
       </c>
       <c r="F181" t="s">
@@ -14590,7 +14546,7 @@
       <c r="D182" t="s">
         <v>622</v>
       </c>
-      <c r="E182" t="s">
+      <c r="E182" s="1" t="s">
         <v>623</v>
       </c>
       <c r="F182" t="s">
@@ -14631,7 +14587,7 @@
       <c r="D183" t="s">
         <v>624</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E183" s="1" t="s">
         <v>581</v>
       </c>
       <c r="F183" t="s">
@@ -14672,7 +14628,7 @@
       <c r="D184" t="s">
         <v>626</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E184" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F184" t="s">
@@ -14713,7 +14669,7 @@
       <c r="D185" t="s">
         <v>493</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E185" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F185" t="s">
@@ -14754,7 +14710,7 @@
       <c r="D186" t="s">
         <v>629</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E186" s="1" t="s">
         <v>630</v>
       </c>
       <c r="F186" t="s">
@@ -14795,7 +14751,7 @@
       <c r="D187" t="s">
         <v>633</v>
       </c>
-      <c r="E187" t="s">
+      <c r="E187" s="1" t="s">
         <v>634</v>
       </c>
       <c r="F187" t="s">
@@ -14836,7 +14792,7 @@
       <c r="D188" t="s">
         <v>637</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E188" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F188" t="s">
@@ -14877,7 +14833,7 @@
       <c r="D189" t="s">
         <v>549</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E189" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F189" t="s">
@@ -14918,7 +14874,7 @@
       <c r="D190" t="s">
         <v>493</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E190" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F190" t="s">
@@ -14959,7 +14915,7 @@
       <c r="D191" t="s">
         <v>641</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E191" s="1" t="s">
         <v>642</v>
       </c>
       <c r="F191" t="s">
@@ -15000,7 +14956,7 @@
       <c r="D192" t="s">
         <v>644</v>
       </c>
-      <c r="E192" t="s">
+      <c r="E192" s="1" t="s">
         <v>645</v>
       </c>
       <c r="F192" t="s">
@@ -15041,7 +14997,7 @@
       <c r="D193" t="s">
         <v>549</v>
       </c>
-      <c r="E193" t="s">
+      <c r="E193" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F193" t="s">
@@ -15082,7 +15038,7 @@
       <c r="D194" t="s">
         <v>648</v>
       </c>
-      <c r="E194" t="s">
+      <c r="E194" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F194" t="s">
@@ -15123,7 +15079,7 @@
       <c r="D195" t="s">
         <v>651</v>
       </c>
-      <c r="E195" t="s">
+      <c r="E195" s="1" t="s">
         <v>652</v>
       </c>
       <c r="F195" t="s">
@@ -15164,7 +15120,7 @@
       <c r="D196" t="s">
         <v>655</v>
       </c>
-      <c r="E196" t="s">
+      <c r="E196" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F196" t="s">
@@ -15205,7 +15161,7 @@
       <c r="D197" t="s">
         <v>657</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E197" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F197" t="s">
@@ -15246,7 +15202,7 @@
       <c r="D198" t="s">
         <v>659</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E198" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F198" t="s">
@@ -15287,7 +15243,7 @@
       <c r="D199" t="s">
         <v>662</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E199" s="1" t="s">
         <v>663</v>
       </c>
       <c r="F199" t="s">
@@ -15328,7 +15284,7 @@
       <c r="D200" t="s">
         <v>665</v>
       </c>
-      <c r="E200" t="s">
+      <c r="E200" s="1" t="s">
         <v>666</v>
       </c>
       <c r="F200" t="s">
@@ -15369,7 +15325,7 @@
       <c r="D201" t="s">
         <v>669</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E201" s="1" t="s">
         <v>670</v>
       </c>
       <c r="F201" t="s">
@@ -15410,7 +15366,7 @@
       <c r="D202" t="s">
         <v>493</v>
       </c>
-      <c r="E202" t="s">
+      <c r="E202" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F202" t="s">
@@ -15451,7 +15407,7 @@
       <c r="D203" t="s">
         <v>673</v>
       </c>
-      <c r="E203" t="s">
+      <c r="E203" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F203" t="s">
@@ -15492,7 +15448,7 @@
       <c r="D204" t="s">
         <v>676</v>
       </c>
-      <c r="E204" t="s">
+      <c r="E204" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F204" t="s">
@@ -15533,7 +15489,7 @@
       <c r="D205" t="s">
         <v>549</v>
       </c>
-      <c r="E205" t="s">
+      <c r="E205" s="1" t="s">
         <v>106</v>
       </c>
       <c r="F205" t="s">
@@ -15574,7 +15530,7 @@
       <c r="D206" t="s">
         <v>681</v>
       </c>
-      <c r="E206" t="s">
+      <c r="E206" s="1" t="s">
         <v>682</v>
       </c>
       <c r="F206" t="s">
@@ -15615,7 +15571,7 @@
       <c r="D207" t="s">
         <v>611</v>
       </c>
-      <c r="E207" t="s">
+      <c r="E207" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F207" t="s">
@@ -15656,7 +15612,7 @@
       <c r="D208" t="s">
         <v>686</v>
       </c>
-      <c r="E208" t="s">
+      <c r="E208" s="1" t="s">
         <v>438</v>
       </c>
       <c r="F208" t="s">
@@ -15697,7 +15653,7 @@
       <c r="D209" t="s">
         <v>689</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E209" s="1" t="s">
         <v>690</v>
       </c>
       <c r="F209" t="s">
@@ -15738,7 +15694,7 @@
       <c r="D210" t="s">
         <v>693</v>
       </c>
-      <c r="E210" t="s">
+      <c r="E210" s="1" t="s">
         <v>434</v>
       </c>
       <c r="F210" t="s">
@@ -15779,7 +15735,7 @@
       <c r="D211" t="s">
         <v>696</v>
       </c>
-      <c r="E211" t="s">
+      <c r="E211" s="1" t="s">
         <v>697</v>
       </c>
       <c r="F211" t="s">
@@ -15820,7 +15776,7 @@
       <c r="D212" t="s">
         <v>699</v>
       </c>
-      <c r="E212" t="s">
+      <c r="E212" s="1" t="s">
         <v>700</v>
       </c>
       <c r="F212" t="s">
@@ -15861,7 +15817,7 @@
       <c r="D213" t="s">
         <v>704</v>
       </c>
-      <c r="E213" t="s">
+      <c r="E213" s="1" t="s">
         <v>705</v>
       </c>
       <c r="F213" t="s">
@@ -15902,7 +15858,7 @@
       <c r="D214" t="s">
         <v>707</v>
       </c>
-      <c r="E214" t="s">
+      <c r="E214" s="1" t="s">
         <v>708</v>
       </c>
       <c r="F214" t="s">
@@ -15943,7 +15899,7 @@
       <c r="D215" t="s">
         <v>711</v>
       </c>
-      <c r="E215" t="s">
+      <c r="E215" s="1" t="s">
         <v>403</v>
       </c>
       <c r="F215" t="s">
@@ -15984,7 +15940,7 @@
       <c r="D216" t="s">
         <v>714</v>
       </c>
-      <c r="E216" t="s">
+      <c r="E216" s="1" t="s">
         <v>715</v>
       </c>
       <c r="F216" t="s">
@@ -16025,7 +15981,7 @@
       <c r="D217" t="s">
         <v>717</v>
       </c>
-      <c r="E217" t="s">
+      <c r="E217" s="1" t="s">
         <v>718</v>
       </c>
       <c r="F217" t="s">
@@ -16066,7 +16022,7 @@
       <c r="D218" t="s">
         <v>720</v>
       </c>
-      <c r="E218" t="s">
+      <c r="E218" s="1" t="s">
         <v>721</v>
       </c>
       <c r="F218" t="s">
@@ -16107,7 +16063,7 @@
       <c r="D219" t="s">
         <v>724</v>
       </c>
-      <c r="E219" t="s">
+      <c r="E219" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F219" t="s">
@@ -16148,7 +16104,7 @@
       <c r="D220" t="s">
         <v>727</v>
       </c>
-      <c r="E220" t="s">
+      <c r="E220" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F220" t="s">
@@ -16189,7 +16145,7 @@
       <c r="D221" t="s">
         <v>493</v>
       </c>
-      <c r="E221" t="s">
+      <c r="E221" s="1" t="s">
         <v>729</v>
       </c>
       <c r="F221" t="s">
@@ -16230,7 +16186,7 @@
       <c r="D222" t="s">
         <v>732</v>
       </c>
-      <c r="E222" t="s">
+      <c r="E222" s="1" t="s">
         <v>733</v>
       </c>
       <c r="F222" t="s">
@@ -16271,7 +16227,7 @@
       <c r="D223" t="s">
         <v>736</v>
       </c>
-      <c r="E223" t="s">
+      <c r="E223" s="1" t="s">
         <v>737</v>
       </c>
       <c r="F223" t="s">
@@ -16312,7 +16268,7 @@
       <c r="D224" t="s">
         <v>740</v>
       </c>
-      <c r="E224" t="s">
+      <c r="E224" s="1" t="s">
         <v>741</v>
       </c>
       <c r="F224" t="s">
@@ -16353,7 +16309,7 @@
       <c r="D225" t="s">
         <v>744</v>
       </c>
-      <c r="E225" t="s">
+      <c r="E225" s="1" t="s">
         <v>745</v>
       </c>
       <c r="F225" t="s">
@@ -16394,7 +16350,7 @@
       <c r="D226" t="s">
         <v>748</v>
       </c>
-      <c r="E226" t="s">
+      <c r="E226" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F226" t="s">
@@ -16435,7 +16391,7 @@
       <c r="D227" t="s">
         <v>751</v>
       </c>
-      <c r="E227" t="s">
+      <c r="E227" s="1" t="s">
         <v>752</v>
       </c>
       <c r="F227" t="s">
@@ -16476,7 +16432,7 @@
       <c r="D228" t="s">
         <v>753</v>
       </c>
-      <c r="E228" t="s">
+      <c r="E228" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F228" t="s">
@@ -16517,7 +16473,7 @@
       <c r="D229" t="s">
         <v>754</v>
       </c>
-      <c r="E229" t="s">
+      <c r="E229" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F229" t="s">
@@ -16558,7 +16514,7 @@
       <c r="D230" t="s">
         <v>757</v>
       </c>
-      <c r="E230" t="s">
+      <c r="E230" s="1" t="s">
         <v>758</v>
       </c>
       <c r="F230" t="s">
@@ -16599,7 +16555,7 @@
       <c r="D231" t="s">
         <v>760</v>
       </c>
-      <c r="E231" t="s">
+      <c r="E231" s="1" t="s">
         <v>761</v>
       </c>
       <c r="F231" t="s">
@@ -16640,7 +16596,7 @@
       <c r="D232" t="s">
         <v>764</v>
       </c>
-      <c r="E232" t="s">
+      <c r="E232" s="1" t="s">
         <v>765</v>
       </c>
       <c r="F232" t="s">
@@ -16681,7 +16637,7 @@
       <c r="D233" t="s">
         <v>766</v>
       </c>
-      <c r="E233" t="s">
+      <c r="E233" s="1" t="s">
         <v>767</v>
       </c>
       <c r="F233" t="s">
@@ -16722,7 +16678,7 @@
       <c r="D234" t="s">
         <v>769</v>
       </c>
-      <c r="E234" t="s">
+      <c r="E234" s="1" t="s">
         <v>770</v>
       </c>
       <c r="F234" t="s">
@@ -16763,7 +16719,7 @@
       <c r="D235" t="s">
         <v>773</v>
       </c>
-      <c r="E235" t="s">
+      <c r="E235" s="1" t="s">
         <v>774</v>
       </c>
       <c r="F235" t="s">
@@ -16804,7 +16760,7 @@
       <c r="D236" t="s">
         <v>777</v>
       </c>
-      <c r="E236" t="s">
+      <c r="E236" s="1" t="s">
         <v>778</v>
       </c>
       <c r="F236" t="s">
@@ -16845,7 +16801,7 @@
       <c r="D237" t="s">
         <v>780</v>
       </c>
-      <c r="E237" t="s">
+      <c r="E237" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F237" t="s">
@@ -16886,7 +16842,7 @@
       <c r="D238" t="s">
         <v>783</v>
       </c>
-      <c r="E238" t="s">
+      <c r="E238" s="1" t="s">
         <v>784</v>
       </c>
       <c r="F238" t="s">
@@ -16927,7 +16883,7 @@
       <c r="D239" t="s">
         <v>787</v>
       </c>
-      <c r="E239" t="s">
+      <c r="E239" s="1" t="s">
         <v>788</v>
       </c>
       <c r="F239" t="s">
@@ -16968,7 +16924,7 @@
       <c r="D240" t="s">
         <v>790</v>
       </c>
-      <c r="E240" t="s">
+      <c r="E240" s="1" t="s">
         <v>791</v>
       </c>
       <c r="F240" t="s">
@@ -17009,7 +16965,7 @@
       <c r="D241" t="s">
         <v>794</v>
       </c>
-      <c r="E241" t="s">
+      <c r="E241" s="1" t="s">
         <v>795</v>
       </c>
       <c r="F241" t="s">
@@ -17050,7 +17006,7 @@
       <c r="D242" t="s">
         <v>493</v>
       </c>
-      <c r="E242" t="s">
+      <c r="E242" s="1" t="s">
         <v>796</v>
       </c>
       <c r="F242" t="s">
@@ -17091,7 +17047,7 @@
       <c r="D243" t="s">
         <v>799</v>
       </c>
-      <c r="E243" t="s">
+      <c r="E243" s="1" t="s">
         <v>800</v>
       </c>
       <c r="F243" t="s">
@@ -17132,7 +17088,7 @@
       <c r="D244" t="s">
         <v>804</v>
       </c>
-      <c r="E244" t="s">
+      <c r="E244" s="1" t="s">
         <v>805</v>
       </c>
       <c r="F244" t="s">
@@ -17173,7 +17129,7 @@
       <c r="D245" t="s">
         <v>807</v>
       </c>
-      <c r="E245" t="s">
+      <c r="E245" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F245" t="s">
@@ -17214,7 +17170,7 @@
       <c r="D246" t="s">
         <v>810</v>
       </c>
-      <c r="E246" t="s">
+      <c r="E246" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F246" t="s">
@@ -17255,7 +17211,7 @@
       <c r="D247" t="s">
         <v>812</v>
       </c>
-      <c r="E247" t="s">
+      <c r="E247" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F247" t="s">
@@ -17296,7 +17252,7 @@
       <c r="D248" t="s">
         <v>815</v>
       </c>
-      <c r="E248" t="s">
+      <c r="E248" s="1" t="s">
         <v>816</v>
       </c>
       <c r="F248" t="s">
@@ -17337,7 +17293,7 @@
       <c r="D249" t="s">
         <v>818</v>
       </c>
-      <c r="E249" t="s">
+      <c r="E249" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F249" t="s">
@@ -17378,7 +17334,7 @@
       <c r="D250" t="s">
         <v>821</v>
       </c>
-      <c r="E250" t="s">
+      <c r="E250" s="1" t="s">
         <v>822</v>
       </c>
       <c r="F250" t="s">
@@ -17419,7 +17375,7 @@
       <c r="D251" t="s">
         <v>826</v>
       </c>
-      <c r="E251" t="s">
+      <c r="E251" s="1" t="s">
         <v>827</v>
       </c>
       <c r="F251" t="s">
@@ -17460,7 +17416,7 @@
       <c r="D252" t="s">
         <v>830</v>
       </c>
-      <c r="E252" t="s">
+      <c r="E252" s="1" t="s">
         <v>831</v>
       </c>
       <c r="F252" t="s">
@@ -17501,7 +17457,7 @@
       <c r="D253" t="s">
         <v>834</v>
       </c>
-      <c r="E253" t="s">
+      <c r="E253" s="1" t="s">
         <v>835</v>
       </c>
       <c r="F253" t="s">
@@ -17542,7 +17498,7 @@
       <c r="D254" t="s">
         <v>838</v>
       </c>
-      <c r="E254" t="s">
+      <c r="E254" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F254" t="s">
@@ -17583,7 +17539,7 @@
       <c r="D255" t="s">
         <v>840</v>
       </c>
-      <c r="E255" t="s">
+      <c r="E255" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F255" t="s">
@@ -17624,7 +17580,7 @@
       <c r="D256" t="s">
         <v>843</v>
       </c>
-      <c r="E256" t="s">
+      <c r="E256" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F256" t="s">
@@ -17665,7 +17621,7 @@
       <c r="D257" t="s">
         <v>846</v>
       </c>
-      <c r="E257" t="s">
+      <c r="E257" s="1" t="s">
         <v>595</v>
       </c>
       <c r="F257" t="s">
@@ -17706,7 +17662,7 @@
       <c r="D258" t="s">
         <v>849</v>
       </c>
-      <c r="E258" t="s">
+      <c r="E258" s="1" t="s">
         <v>850</v>
       </c>
       <c r="F258" t="s">
@@ -17747,7 +17703,7 @@
       <c r="D259" t="s">
         <v>853</v>
       </c>
-      <c r="E259" t="s">
+      <c r="E259" s="1" t="s">
         <v>854</v>
       </c>
       <c r="F259" t="s">
@@ -17788,7 +17744,7 @@
       <c r="D260" t="s">
         <v>858</v>
       </c>
-      <c r="E260" t="s">
+      <c r="E260" s="1" t="s">
         <v>859</v>
       </c>
       <c r="F260" t="s">
@@ -17829,7 +17785,7 @@
       <c r="D261" t="s">
         <v>861</v>
       </c>
-      <c r="E261" t="s">
+      <c r="E261" s="1" t="s">
         <v>862</v>
       </c>
       <c r="F261" t="s">
@@ -17870,7 +17826,7 @@
       <c r="D262" t="s">
         <v>865</v>
       </c>
-      <c r="E262" t="s">
+      <c r="E262" s="1" t="s">
         <v>866</v>
       </c>
       <c r="F262" t="s">
@@ -17911,7 +17867,7 @@
       <c r="D263" t="s">
         <v>869</v>
       </c>
-      <c r="E263" t="s">
+      <c r="E263" s="1" t="s">
         <v>870</v>
       </c>
       <c r="F263" t="s">
@@ -17952,7 +17908,7 @@
       <c r="D264" t="s">
         <v>873</v>
       </c>
-      <c r="E264" t="s">
+      <c r="E264" s="1" t="s">
         <v>874</v>
       </c>
       <c r="F264" t="s">
@@ -17993,7 +17949,7 @@
       <c r="D265" t="s">
         <v>877</v>
       </c>
-      <c r="E265" t="s">
+      <c r="E265" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F265" t="s">
@@ -18034,7 +17990,7 @@
       <c r="D266" t="s">
         <v>879</v>
       </c>
-      <c r="E266" t="s">
+      <c r="E266" s="1" t="s">
         <v>880</v>
       </c>
       <c r="F266" t="s">
@@ -18075,7 +18031,7 @@
       <c r="D267" t="s">
         <v>493</v>
       </c>
-      <c r="E267" t="s">
+      <c r="E267" s="1" t="s">
         <v>882</v>
       </c>
       <c r="F267" t="s">
@@ -18116,7 +18072,7 @@
       <c r="D268" t="s">
         <v>884</v>
       </c>
-      <c r="E268" t="s">
+      <c r="E268" s="1" t="s">
         <v>885</v>
       </c>
       <c r="F268" t="s">
@@ -18157,7 +18113,7 @@
       <c r="D269" t="s">
         <v>888</v>
       </c>
-      <c r="E269" t="s">
+      <c r="E269" s="1" t="s">
         <v>269</v>
       </c>
       <c r="F269" t="s">
@@ -18198,7 +18154,7 @@
       <c r="D270" t="s">
         <v>890</v>
       </c>
-      <c r="E270" t="s">
+      <c r="E270" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F270" t="s">
@@ -18239,7 +18195,7 @@
       <c r="D271" t="s">
         <v>892</v>
       </c>
-      <c r="E271" t="s">
+      <c r="E271" s="1" t="s">
         <v>893</v>
       </c>
       <c r="F271" t="s">
@@ -18280,7 +18236,7 @@
       <c r="D272" t="s">
         <v>896</v>
       </c>
-      <c r="E272" t="s">
+      <c r="E272" s="1" t="s">
         <v>897</v>
       </c>
       <c r="F272" t="s">
@@ -18321,7 +18277,7 @@
       <c r="D273" t="s">
         <v>899</v>
       </c>
-      <c r="E273" t="s">
+      <c r="E273" s="1" t="s">
         <v>900</v>
       </c>
       <c r="F273" t="s">
@@ -18362,7 +18318,7 @@
       <c r="D274" t="s">
         <v>903</v>
       </c>
-      <c r="E274" t="s">
+      <c r="E274" s="1" t="s">
         <v>904</v>
       </c>
       <c r="F274" t="s">
@@ -18403,7 +18359,7 @@
       <c r="D275" t="s">
         <v>907</v>
       </c>
-      <c r="E275" t="s">
+      <c r="E275" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F275" t="s">
@@ -18444,7 +18400,7 @@
       <c r="D276" t="s">
         <v>909</v>
       </c>
-      <c r="E276" t="s">
+      <c r="E276" s="1" t="s">
         <v>910</v>
       </c>
       <c r="F276" t="s">
@@ -18485,7 +18441,7 @@
       <c r="D277" t="s">
         <v>913</v>
       </c>
-      <c r="E277" t="s">
+      <c r="E277" s="1" t="s">
         <v>217</v>
       </c>
       <c r="F277" t="s">
@@ -18526,7 +18482,7 @@
       <c r="D278" t="s">
         <v>916</v>
       </c>
-      <c r="E278" t="s">
+      <c r="E278" s="1" t="s">
         <v>917</v>
       </c>
       <c r="F278" t="s">
@@ -18567,7 +18523,7 @@
       <c r="D279" t="s">
         <v>920</v>
       </c>
-      <c r="E279" t="s">
+      <c r="E279" s="1" t="s">
         <v>921</v>
       </c>
       <c r="F279" t="s">
@@ -18608,7 +18564,7 @@
       <c r="D280" t="s">
         <v>757</v>
       </c>
-      <c r="E280" t="s">
+      <c r="E280" s="1" t="s">
         <v>924</v>
       </c>
       <c r="F280" t="s">
@@ -18649,7 +18605,7 @@
       <c r="D281" t="s">
         <v>493</v>
       </c>
-      <c r="E281" t="s">
+      <c r="E281" s="1" t="s">
         <v>926</v>
       </c>
       <c r="F281" t="s">
@@ -18690,7 +18646,7 @@
       <c r="D282" t="s">
         <v>928</v>
       </c>
-      <c r="E282" t="s">
+      <c r="E282" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F282" t="s">
@@ -18731,7 +18687,7 @@
       <c r="D283" t="s">
         <v>930</v>
       </c>
-      <c r="E283" t="s">
+      <c r="E283" s="1" t="s">
         <v>931</v>
       </c>
       <c r="F283" t="s">
@@ -18772,7 +18728,7 @@
       <c r="D284" t="s">
         <v>934</v>
       </c>
-      <c r="E284" t="s">
+      <c r="E284" s="1" t="s">
         <v>935</v>
       </c>
       <c r="F284" t="s">
@@ -18813,7 +18769,7 @@
       <c r="D285" t="s">
         <v>937</v>
       </c>
-      <c r="E285" t="s">
+      <c r="E285" s="1" t="s">
         <v>938</v>
       </c>
       <c r="F285" t="s">
@@ -18854,7 +18810,7 @@
       <c r="D286" t="s">
         <v>940</v>
       </c>
-      <c r="E286" t="s">
+      <c r="E286" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F286" t="s">
@@ -18895,7 +18851,7 @@
       <c r="D287" t="s">
         <v>944</v>
       </c>
-      <c r="E287" t="s">
+      <c r="E287" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F287" t="s">
@@ -18936,7 +18892,7 @@
       <c r="D288" t="s">
         <v>948</v>
       </c>
-      <c r="E288" t="s">
+      <c r="E288" s="1" t="s">
         <v>949</v>
       </c>
       <c r="F288" t="s">
@@ -18977,7 +18933,7 @@
       <c r="D289" t="s">
         <v>952</v>
       </c>
-      <c r="E289" t="s">
+      <c r="E289" s="1" t="s">
         <v>953</v>
       </c>
       <c r="F289" t="s">
@@ -19018,7 +18974,7 @@
       <c r="D290" t="s">
         <v>280</v>
       </c>
-      <c r="E290" t="s">
+      <c r="E290" s="1" t="s">
         <v>956</v>
       </c>
       <c r="F290" t="s">
@@ -19059,7 +19015,7 @@
       <c r="D291" t="s">
         <v>959</v>
       </c>
-      <c r="E291" t="s">
+      <c r="E291" s="1" t="s">
         <v>960</v>
       </c>
       <c r="F291" t="s">
@@ -19100,7 +19056,7 @@
       <c r="D292" t="s">
         <v>962</v>
       </c>
-      <c r="E292" t="s">
+      <c r="E292" s="1" t="s">
         <v>963</v>
       </c>
       <c r="F292" t="s">
@@ -19141,7 +19097,7 @@
       <c r="D293" t="s">
         <v>966</v>
       </c>
-      <c r="E293" t="s">
+      <c r="E293" s="1" t="s">
         <v>967</v>
       </c>
       <c r="F293" t="s">
@@ -19182,7 +19138,7 @@
       <c r="D294" t="s">
         <v>970</v>
       </c>
-      <c r="E294" t="s">
+      <c r="E294" s="1" t="s">
         <v>971</v>
       </c>
       <c r="F294" t="s">
@@ -19223,7 +19179,7 @@
       <c r="D295" t="s">
         <v>973</v>
       </c>
-      <c r="E295" t="s">
+      <c r="E295" s="1" t="s">
         <v>974</v>
       </c>
       <c r="F295" t="s">
@@ -19264,7 +19220,7 @@
       <c r="D296" t="s">
         <v>977</v>
       </c>
-      <c r="E296" t="s">
+      <c r="E296" s="1" t="s">
         <v>978</v>
       </c>
       <c r="F296" t="s">
@@ -19305,7 +19261,7 @@
       <c r="D297" t="s">
         <v>981</v>
       </c>
-      <c r="E297" t="s">
+      <c r="E297" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F297" t="s">
@@ -19346,7 +19302,7 @@
       <c r="D298" t="s">
         <v>983</v>
       </c>
-      <c r="E298" t="s">
+      <c r="E298" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F298" t="s">
@@ -19387,7 +19343,7 @@
       <c r="D299" t="s">
         <v>986</v>
       </c>
-      <c r="E299" t="s">
+      <c r="E299" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F299" t="s">
@@ -19428,7 +19384,7 @@
       <c r="D300" t="s">
         <v>988</v>
       </c>
-      <c r="E300" t="s">
+      <c r="E300" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F300" t="s">
@@ -19469,7 +19425,7 @@
       <c r="D301" t="s">
         <v>990</v>
       </c>
-      <c r="E301" t="s">
+      <c r="E301" s="1" t="s">
         <v>991</v>
       </c>
       <c r="F301" t="s">
@@ -19510,7 +19466,7 @@
       <c r="D302" t="s">
         <v>995</v>
       </c>
-      <c r="E302" t="s">
+      <c r="E302" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F302" t="s">
@@ -19551,7 +19507,7 @@
       <c r="D303" t="s">
         <v>998</v>
       </c>
-      <c r="E303" t="s">
+      <c r="E303" s="1" t="s">
         <v>438</v>
       </c>
       <c r="F303" t="s">
@@ -19592,7 +19548,7 @@
       <c r="D304" t="s">
         <v>1001</v>
       </c>
-      <c r="E304" t="s">
+      <c r="E304" s="1" t="s">
         <v>595</v>
       </c>
       <c r="F304" t="s">
@@ -19633,7 +19589,7 @@
       <c r="D305" t="s">
         <v>696</v>
       </c>
-      <c r="E305" t="s">
+      <c r="E305" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F305" t="s">
@@ -19674,7 +19630,7 @@
       <c r="D306" t="s">
         <v>1006</v>
       </c>
-      <c r="E306" t="s">
+      <c r="E306" s="1" t="s">
         <v>1007</v>
       </c>
       <c r="F306" t="s">
@@ -19715,7 +19671,7 @@
       <c r="D307" t="s">
         <v>1010</v>
       </c>
-      <c r="E307" t="s">
+      <c r="E307" s="1" t="s">
         <v>1011</v>
       </c>
       <c r="F307" t="s">
@@ -19756,7 +19712,7 @@
       <c r="D308" t="s">
         <v>1015</v>
       </c>
-      <c r="E308" t="s">
+      <c r="E308" s="1" t="s">
         <v>1016</v>
       </c>
       <c r="F308" t="s">
@@ -19797,7 +19753,7 @@
       <c r="D309" t="s">
         <v>1019</v>
       </c>
-      <c r="E309" t="s">
+      <c r="E309" s="1" t="s">
         <v>1020</v>
       </c>
       <c r="F309" t="s">
@@ -19838,7 +19794,7 @@
       <c r="D310" t="s">
         <v>280</v>
       </c>
-      <c r="E310" t="s">
+      <c r="E310" s="1" t="s">
         <v>1024</v>
       </c>
       <c r="F310" t="s">
@@ -19879,7 +19835,7 @@
       <c r="D311" t="s">
         <v>1026</v>
       </c>
-      <c r="E311" t="s">
+      <c r="E311" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F311" t="s">
@@ -19920,7 +19876,7 @@
       <c r="D312" t="s">
         <v>120</v>
       </c>
-      <c r="E312" t="s">
+      <c r="E312" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F312" t="s">
@@ -19961,7 +19917,7 @@
       <c r="D313" t="s">
         <v>696</v>
       </c>
-      <c r="E313" t="s">
+      <c r="E313" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F313" t="s">
@@ -20002,7 +19958,7 @@
       <c r="D314" t="s">
         <v>1031</v>
       </c>
-      <c r="E314" t="s">
+      <c r="E314" s="1" t="s">
         <v>1032</v>
       </c>
       <c r="F314" t="s">
@@ -20043,7 +19999,7 @@
       <c r="D315" t="s">
         <v>1034</v>
       </c>
-      <c r="E315" t="s">
+      <c r="E315" s="1" t="s">
         <v>1035</v>
       </c>
       <c r="F315" t="s">
@@ -20084,7 +20040,7 @@
       <c r="D316" t="s">
         <v>1037</v>
       </c>
-      <c r="E316" t="s">
+      <c r="E316" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F316" t="s">
@@ -20125,7 +20081,7 @@
       <c r="D317" t="s">
         <v>1040</v>
       </c>
-      <c r="E317" t="s">
+      <c r="E317" s="1" t="s">
         <v>1041</v>
       </c>
       <c r="F317" t="s">
@@ -20166,7 +20122,7 @@
       <c r="D318" t="s">
         <v>1044</v>
       </c>
-      <c r="E318" t="s">
+      <c r="E318" s="1" t="s">
         <v>1045</v>
       </c>
       <c r="F318" t="s">
@@ -20207,7 +20163,7 @@
       <c r="D319" t="s">
         <v>1048</v>
       </c>
-      <c r="E319" t="s">
+      <c r="E319" s="1" t="s">
         <v>1049</v>
       </c>
       <c r="F319" t="s">
@@ -20248,7 +20204,7 @@
       <c r="D320" t="s">
         <v>1052</v>
       </c>
-      <c r="E320" t="s">
+      <c r="E320" s="1" t="s">
         <v>1053</v>
       </c>
       <c r="F320" t="s">
@@ -20289,7 +20245,7 @@
       <c r="D321" t="s">
         <v>1056</v>
       </c>
-      <c r="E321" t="s">
+      <c r="E321" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F321" t="s">
@@ -20330,7 +20286,7 @@
       <c r="D322" t="s">
         <v>1058</v>
       </c>
-      <c r="E322" t="s">
+      <c r="E322" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F322" t="s">
@@ -20371,7 +20327,7 @@
       <c r="D323" t="s">
         <v>1060</v>
       </c>
-      <c r="E323" t="s">
+      <c r="E323" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F323" t="s">
@@ -20412,7 +20368,7 @@
       <c r="D324" t="s">
         <v>1063</v>
       </c>
-      <c r="E324" t="s">
+      <c r="E324" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F324" t="s">
@@ -20453,7 +20409,7 @@
       <c r="D325" t="s">
         <v>1066</v>
       </c>
-      <c r="E325" t="s">
+      <c r="E325" s="1" t="s">
         <v>1067</v>
       </c>
       <c r="F325" t="s">
@@ -20494,7 +20450,7 @@
       <c r="D326" t="s">
         <v>696</v>
       </c>
-      <c r="E326" t="s">
+      <c r="E326" s="1" t="s">
         <v>1069</v>
       </c>
       <c r="F326" t="s">
@@ -20535,7 +20491,7 @@
       <c r="D327" t="s">
         <v>1070</v>
       </c>
-      <c r="E327" t="s">
+      <c r="E327" s="1" t="s">
         <v>1071</v>
       </c>
       <c r="F327" t="s">
@@ -20576,7 +20532,7 @@
       <c r="D328" t="s">
         <v>1073</v>
       </c>
-      <c r="E328" t="s">
+      <c r="E328" s="1" t="s">
         <v>1074</v>
       </c>
       <c r="F328" t="s">
@@ -20617,7 +20573,7 @@
       <c r="D329" t="s">
         <v>1077</v>
       </c>
-      <c r="E329" t="s">
+      <c r="E329" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F329" t="s">
@@ -20658,7 +20614,7 @@
       <c r="D330" t="s">
         <v>1079</v>
       </c>
-      <c r="E330" t="s">
+      <c r="E330" s="1" t="s">
         <v>1080</v>
       </c>
       <c r="F330" t="s">
@@ -20699,7 +20655,7 @@
       <c r="D331" t="s">
         <v>1082</v>
       </c>
-      <c r="E331" t="s">
+      <c r="E331" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F331" t="s">
@@ -20740,7 +20696,7 @@
       <c r="D332" t="s">
         <v>1086</v>
       </c>
-      <c r="E332" t="s">
+      <c r="E332" s="1" t="s">
         <v>1087</v>
       </c>
       <c r="F332" t="s">
@@ -20781,7 +20737,7 @@
       <c r="D333" t="s">
         <v>1089</v>
       </c>
-      <c r="E333" t="s">
+      <c r="E333" s="1" t="s">
         <v>1090</v>
       </c>
       <c r="F333" t="s">
@@ -20822,7 +20778,7 @@
       <c r="D334" t="s">
         <v>1093</v>
       </c>
-      <c r="E334" t="s">
+      <c r="E334" s="1" t="s">
         <v>1094</v>
       </c>
       <c r="F334" t="s">
@@ -20863,7 +20819,7 @@
       <c r="D335" t="s">
         <v>1097</v>
       </c>
-      <c r="E335" t="s">
+      <c r="E335" s="1" t="s">
         <v>1098</v>
       </c>
       <c r="F335" t="s">
@@ -20904,7 +20860,7 @@
       <c r="D336" t="s">
         <v>1100</v>
       </c>
-      <c r="E336" t="s">
+      <c r="E336" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F336" t="s">
@@ -20945,7 +20901,7 @@
       <c r="D337" t="s">
         <v>1103</v>
       </c>
-      <c r="E337" t="s">
+      <c r="E337" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F337" t="s">
@@ -20986,7 +20942,7 @@
       <c r="D338" t="s">
         <v>1105</v>
       </c>
-      <c r="E338" t="s">
+      <c r="E338" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F338" t="s">
@@ -21027,7 +20983,7 @@
       <c r="D339" t="s">
         <v>696</v>
       </c>
-      <c r="E339" t="s">
+      <c r="E339" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F339" t="s">
@@ -21068,7 +21024,7 @@
       <c r="D340" t="s">
         <v>280</v>
       </c>
-      <c r="E340" t="s">
+      <c r="E340" s="1" t="s">
         <v>1110</v>
       </c>
       <c r="F340" t="s">
@@ -21109,7 +21065,7 @@
       <c r="D341" t="s">
         <v>1112</v>
       </c>
-      <c r="E341" t="s">
+      <c r="E341" s="1" t="s">
         <v>1113</v>
       </c>
       <c r="F341" t="s">
@@ -21150,7 +21106,7 @@
       <c r="D342" t="s">
         <v>1117</v>
       </c>
-      <c r="E342" t="s">
+      <c r="E342" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="F342" t="s">
@@ -21191,7 +21147,7 @@
       <c r="D343" t="s">
         <v>1093</v>
       </c>
-      <c r="E343" t="s">
+      <c r="E343" s="1" t="s">
         <v>1094</v>
       </c>
       <c r="F343" t="s">
@@ -21232,7 +21188,7 @@
       <c r="D344" t="s">
         <v>1122</v>
       </c>
-      <c r="E344" t="s">
+      <c r="E344" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F344" t="s">
@@ -21273,7 +21229,7 @@
       <c r="D345" t="s">
         <v>1125</v>
       </c>
-      <c r="E345" t="s">
+      <c r="E345" s="1" t="s">
         <v>893</v>
       </c>
       <c r="F345" t="s">
@@ -21314,7 +21270,7 @@
       <c r="D346" t="s">
         <v>1128</v>
       </c>
-      <c r="E346" t="s">
+      <c r="E346" s="1" t="s">
         <v>1129</v>
       </c>
       <c r="F346" t="s">
@@ -21355,7 +21311,7 @@
       <c r="D347" t="s">
         <v>1131</v>
       </c>
-      <c r="E347" t="s">
+      <c r="E347" s="1" t="s">
         <v>150</v>
       </c>
       <c r="F347" t="s">
@@ -21396,7 +21352,7 @@
       <c r="D348" t="s">
         <v>1133</v>
       </c>
-      <c r="E348" t="s">
+      <c r="E348" s="1" t="s">
         <v>1134</v>
       </c>
       <c r="F348" t="s">
@@ -21437,7 +21393,7 @@
       <c r="D349" t="s">
         <v>696</v>
       </c>
-      <c r="E349" t="s">
+      <c r="E349" s="1" t="s">
         <v>1137</v>
       </c>
       <c r="F349" t="s">
@@ -21478,7 +21434,7 @@
       <c r="D350" t="s">
         <v>1139</v>
       </c>
-      <c r="E350" t="s">
+      <c r="E350" s="1" t="s">
         <v>1140</v>
       </c>
       <c r="F350" t="s">
@@ -21519,7 +21475,7 @@
       <c r="D351" t="s">
         <v>1143</v>
       </c>
-      <c r="E351" t="s">
+      <c r="E351" s="1" t="s">
         <v>196</v>
       </c>
       <c r="F351" t="s">
@@ -21560,7 +21516,7 @@
       <c r="D352" t="s">
         <v>1146</v>
       </c>
-      <c r="E352" t="s">
+      <c r="E352" s="1" t="s">
         <v>1147</v>
       </c>
       <c r="F352" t="s">
@@ -21601,7 +21557,7 @@
       <c r="D353" t="s">
         <v>1149</v>
       </c>
-      <c r="E353" t="s">
+      <c r="E353" s="1" t="s">
         <v>1150</v>
       </c>
       <c r="F353" t="s">
@@ -21642,7 +21598,7 @@
       <c r="D354" t="s">
         <v>1152</v>
       </c>
-      <c r="E354" t="s">
+      <c r="E354" s="1" t="s">
         <v>1153</v>
       </c>
       <c r="F354" t="s">
@@ -21683,7 +21639,7 @@
       <c r="D355" t="s">
         <v>1156</v>
       </c>
-      <c r="E355" t="s">
+      <c r="E355" s="1" t="s">
         <v>1157</v>
       </c>
       <c r="F355" t="s">
@@ -21724,7 +21680,7 @@
       <c r="D356" t="s">
         <v>1142</v>
       </c>
-      <c r="E356" t="s">
+      <c r="E356" s="1" t="s">
         <v>1158</v>
       </c>
       <c r="F356" t="s">
@@ -21765,7 +21721,7 @@
       <c r="D357" t="s">
         <v>1142</v>
       </c>
-      <c r="E357" t="s">
+      <c r="E357" s="1" t="s">
         <v>1159</v>
       </c>
       <c r="F357" t="s">
@@ -21806,7 +21762,7 @@
       <c r="D358" t="s">
         <v>1162</v>
       </c>
-      <c r="E358" t="s">
+      <c r="E358" s="1" t="s">
         <v>1163</v>
       </c>
       <c r="F358" t="s">
@@ -21847,7 +21803,7 @@
       <c r="D359" t="s">
         <v>1165</v>
       </c>
-      <c r="E359" t="s">
+      <c r="E359" s="1" t="s">
         <v>1166</v>
       </c>
       <c r="F359" t="s">
@@ -21888,7 +21844,7 @@
       <c r="D360" t="s">
         <v>1169</v>
       </c>
-      <c r="E360" t="s">
+      <c r="E360" s="1" t="s">
         <v>1170</v>
       </c>
       <c r="F360" t="s">
@@ -21929,7 +21885,7 @@
       <c r="D361" t="s">
         <v>1173</v>
       </c>
-      <c r="E361" t="s">
+      <c r="E361" s="1" t="s">
         <v>1174</v>
       </c>
       <c r="F361" t="s">
@@ -21970,7 +21926,7 @@
       <c r="D362" t="s">
         <v>1176</v>
       </c>
-      <c r="E362" t="s">
+      <c r="E362" s="1" t="s">
         <v>1177</v>
       </c>
       <c r="F362" t="s">
@@ -22011,7 +21967,7 @@
       <c r="D363" t="s">
         <v>1180</v>
       </c>
-      <c r="E363" t="s">
+      <c r="E363" s="1" t="s">
         <v>1181</v>
       </c>
       <c r="F363" t="s">
@@ -22052,7 +22008,7 @@
       <c r="D364" t="s">
         <v>1184</v>
       </c>
-      <c r="E364" t="s">
+      <c r="E364" s="1" t="s">
         <v>1185</v>
       </c>
       <c r="F364" t="s">
@@ -22093,7 +22049,7 @@
       <c r="D365" t="s">
         <v>1187</v>
       </c>
-      <c r="E365" t="s">
+      <c r="E365" s="1" t="s">
         <v>1188</v>
       </c>
       <c r="F365" t="s">
@@ -22134,7 +22090,7 @@
       <c r="D366" t="s">
         <v>1191</v>
       </c>
-      <c r="E366" t="s">
+      <c r="E366" s="1" t="s">
         <v>1192</v>
       </c>
       <c r="F366" t="s">
@@ -22175,7 +22131,7 @@
       <c r="D367" t="s">
         <v>1193</v>
       </c>
-      <c r="E367" t="s">
+      <c r="E367" s="1" t="s">
         <v>1194</v>
       </c>
       <c r="F367" t="s">
@@ -22216,7 +22172,7 @@
       <c r="D368" t="s">
         <v>1196</v>
       </c>
-      <c r="E368" t="s">
+      <c r="E368" s="1" t="s">
         <v>1197</v>
       </c>
       <c r="F368" t="s">
@@ -22257,7 +22213,7 @@
       <c r="D369" t="s">
         <v>1200</v>
       </c>
-      <c r="E369" t="s">
+      <c r="E369" s="1" t="s">
         <v>1201</v>
       </c>
       <c r="F369" t="s">
@@ -22298,7 +22254,7 @@
       <c r="D370" t="s">
         <v>1204</v>
       </c>
-      <c r="E370" t="s">
+      <c r="E370" s="1" t="s">
         <v>1205</v>
       </c>
       <c r="F370" t="s">
@@ -22339,7 +22295,7 @@
       <c r="D371" t="s">
         <v>1207</v>
       </c>
-      <c r="E371" t="s">
+      <c r="E371" s="1" t="s">
         <v>1208</v>
       </c>
       <c r="F371" t="s">
@@ -22380,7 +22336,7 @@
       <c r="D372" t="s">
         <v>1210</v>
       </c>
-      <c r="E372" t="s">
+      <c r="E372" s="1" t="s">
         <v>1211</v>
       </c>
       <c r="F372" t="s">
@@ -22421,7 +22377,7 @@
       <c r="D373" t="s">
         <v>1214</v>
       </c>
-      <c r="E373" t="s">
+      <c r="E373" s="1" t="s">
         <v>1215</v>
       </c>
       <c r="F373" t="s">
@@ -22462,7 +22418,7 @@
       <c r="D374" t="s">
         <v>1217</v>
       </c>
-      <c r="E374" t="s">
+      <c r="E374" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F374" t="s">
@@ -22503,7 +22459,7 @@
       <c r="D375" t="s">
         <v>1220</v>
       </c>
-      <c r="E375" t="s">
+      <c r="E375" s="1" t="s">
         <v>1221</v>
       </c>
       <c r="F375" t="s">
@@ -22544,7 +22500,7 @@
       <c r="D376" t="s">
         <v>1224</v>
       </c>
-      <c r="E376" t="s">
+      <c r="E376" s="1" t="s">
         <v>1225</v>
       </c>
       <c r="F376" t="s">
@@ -22585,7 +22541,7 @@
       <c r="D377" t="s">
         <v>1228</v>
       </c>
-      <c r="E377" t="s">
+      <c r="E377" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F377" t="s">
@@ -22626,7 +22582,7 @@
       <c r="D378" t="s">
         <v>1230</v>
       </c>
-      <c r="E378" t="s">
+      <c r="E378" s="1" t="s">
         <v>1231</v>
       </c>
       <c r="F378" t="s">
@@ -22667,7 +22623,7 @@
       <c r="D379" t="s">
         <v>1234</v>
       </c>
-      <c r="E379" t="s">
+      <c r="E379" s="1" t="s">
         <v>1235</v>
       </c>
       <c r="F379" t="s">
@@ -22708,7 +22664,7 @@
       <c r="D380" t="s">
         <v>1237</v>
       </c>
-      <c r="E380" t="s">
+      <c r="E380" s="1" t="s">
         <v>1238</v>
       </c>
       <c r="F380" t="s">
@@ -22749,7 +22705,7 @@
       <c r="D381" t="s">
         <v>1240</v>
       </c>
-      <c r="E381" t="s">
+      <c r="E381" s="1" t="s">
         <v>1241</v>
       </c>
       <c r="F381" t="s">
@@ -22790,7 +22746,7 @@
       <c r="D382" t="s">
         <v>1243</v>
       </c>
-      <c r="E382" t="s">
+      <c r="E382" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F382" t="s">
@@ -22831,7 +22787,7 @@
       <c r="D383" t="s">
         <v>1207</v>
       </c>
-      <c r="E383" t="s">
+      <c r="E383" s="1" t="s">
         <v>1244</v>
       </c>
       <c r="F383" t="s">
@@ -22872,7 +22828,7 @@
       <c r="D384" t="s">
         <v>1247</v>
       </c>
-      <c r="E384" t="s">
+      <c r="E384" s="1" t="s">
         <v>1248</v>
       </c>
       <c r="F384" t="s">
@@ -22913,7 +22869,7 @@
       <c r="D385" t="s">
         <v>1097</v>
       </c>
-      <c r="E385" t="s">
+      <c r="E385" s="1" t="s">
         <v>1250</v>
       </c>
       <c r="F385" t="s">
@@ -22954,7 +22910,7 @@
       <c r="D386" t="s">
         <v>1207</v>
       </c>
-      <c r="E386" t="s">
+      <c r="E386" s="1" t="s">
         <v>1252</v>
       </c>
       <c r="F386" t="s">
@@ -22995,7 +22951,7 @@
       <c r="D387" t="s">
         <v>1255</v>
       </c>
-      <c r="E387" t="s">
+      <c r="E387" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F387" t="s">
@@ -23036,7 +22992,7 @@
       <c r="D388" t="s">
         <v>1258</v>
       </c>
-      <c r="E388" t="s">
+      <c r="E388" s="1" t="s">
         <v>1259</v>
       </c>
       <c r="F388" t="s">
@@ -23077,7 +23033,7 @@
       <c r="D389" t="s">
         <v>1261</v>
       </c>
-      <c r="E389" t="s">
+      <c r="E389" s="1" t="s">
         <v>1262</v>
       </c>
       <c r="F389" t="s">
@@ -23118,7 +23074,7 @@
       <c r="D390" t="s">
         <v>1265</v>
       </c>
-      <c r="E390" t="s">
+      <c r="E390" s="1" t="s">
         <v>1266</v>
       </c>
       <c r="F390" t="s">
@@ -23159,7 +23115,7 @@
       <c r="D391" t="s">
         <v>1268</v>
       </c>
-      <c r="E391" t="s">
+      <c r="E391" s="1" t="s">
         <v>941</v>
       </c>
       <c r="F391" t="s">
@@ -23200,7 +23156,7 @@
       <c r="D392" t="s">
         <v>1270</v>
       </c>
-      <c r="E392" t="s">
+      <c r="E392" s="1" t="s">
         <v>1271</v>
       </c>
       <c r="F392" t="s">
@@ -23241,7 +23197,7 @@
       <c r="D393" t="s">
         <v>1274</v>
       </c>
-      <c r="E393" t="s">
+      <c r="E393" s="1" t="s">
         <v>1275</v>
       </c>
       <c r="F393" t="s">
@@ -23282,7 +23238,7 @@
       <c r="D394" t="s">
         <v>1277</v>
       </c>
-      <c r="E394" t="s">
+      <c r="E394" s="1" t="s">
         <v>433</v>
       </c>
       <c r="F394" t="s">
@@ -23323,7 +23279,7 @@
       <c r="D395" t="s">
         <v>1280</v>
       </c>
-      <c r="E395" t="s">
+      <c r="E395" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F395" t="s">
@@ -23364,7 +23320,7 @@
       <c r="D396" t="s">
         <v>1282</v>
       </c>
-      <c r="E396" t="s">
+      <c r="E396" s="1" t="s">
         <v>1283</v>
       </c>
       <c r="F396" t="s">
@@ -23405,7 +23361,7 @@
       <c r="D397" t="s">
         <v>1286</v>
       </c>
-      <c r="E397" t="s">
+      <c r="E397" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F397" t="s">
@@ -23446,7 +23402,7 @@
       <c r="D398" t="s">
         <v>1289</v>
       </c>
-      <c r="E398" t="s">
+      <c r="E398" s="1" t="s">
         <v>1290</v>
       </c>
       <c r="F398" t="s">
@@ -23487,7 +23443,7 @@
       <c r="D399" t="s">
         <v>1293</v>
       </c>
-      <c r="E399" t="s">
+      <c r="E399" s="1" t="s">
         <v>1294</v>
       </c>
       <c r="F399" t="s">
@@ -23528,7 +23484,7 @@
       <c r="D400" t="s">
         <v>1297</v>
       </c>
-      <c r="E400" t="s">
+      <c r="E400" s="1" t="s">
         <v>1298</v>
       </c>
       <c r="F400" t="s">
@@ -23569,7 +23525,7 @@
       <c r="D401" t="s">
         <v>1300</v>
       </c>
-      <c r="E401" t="s">
+      <c r="E401" s="1" t="s">
         <v>1301</v>
       </c>
       <c r="F401" t="s">
@@ -23610,7 +23566,7 @@
       <c r="D402" t="s">
         <v>1303</v>
       </c>
-      <c r="E402" t="s">
+      <c r="E402" s="1" t="s">
         <v>1304</v>
       </c>
       <c r="F402" t="s">
@@ -23651,7 +23607,7 @@
       <c r="D403" t="s">
         <v>1306</v>
       </c>
-      <c r="E403" t="s">
+      <c r="E403" s="1" t="s">
         <v>1307</v>
       </c>
       <c r="F403" t="s">
@@ -23692,7 +23648,7 @@
       <c r="D404" t="s">
         <v>1309</v>
       </c>
-      <c r="E404" t="s">
+      <c r="E404" s="1" t="s">
         <v>1310</v>
       </c>
       <c r="F404" t="s">
@@ -23733,7 +23689,7 @@
       <c r="D405" t="s">
         <v>1312</v>
       </c>
-      <c r="E405" t="s">
+      <c r="E405" s="1" t="s">
         <v>1313</v>
       </c>
       <c r="F405" t="s">
@@ -23774,7 +23730,7 @@
       <c r="D406" t="s">
         <v>1315</v>
       </c>
-      <c r="E406" t="s">
+      <c r="E406" s="1" t="s">
         <v>1316</v>
       </c>
       <c r="F406" t="s">
@@ -23815,7 +23771,7 @@
       <c r="D407" t="s">
         <v>280</v>
       </c>
-      <c r="E407" t="s">
+      <c r="E407" s="1" t="s">
         <v>1317</v>
       </c>
       <c r="F407" t="s">
@@ -23856,7 +23812,7 @@
       <c r="D408" t="s">
         <v>1320</v>
       </c>
-      <c r="E408" t="s">
+      <c r="E408" s="1" t="s">
         <v>1321</v>
       </c>
       <c r="F408" t="s">
@@ -23897,7 +23853,7 @@
       <c r="D409" t="s">
         <v>1324</v>
       </c>
-      <c r="E409" t="s">
+      <c r="E409" s="1" t="s">
         <v>1325</v>
       </c>
       <c r="F409" t="s">
@@ -23938,7 +23894,7 @@
       <c r="D410" t="s">
         <v>1327</v>
       </c>
-      <c r="E410" t="s">
+      <c r="E410" s="1" t="s">
         <v>1328</v>
       </c>
       <c r="F410" t="s">
@@ -23979,7 +23935,7 @@
       <c r="D411" t="s">
         <v>1330</v>
       </c>
-      <c r="E411" t="s">
+      <c r="E411" s="1" t="s">
         <v>1331</v>
       </c>
       <c r="F411" t="s">
@@ -24020,7 +23976,7 @@
       <c r="D412" t="s">
         <v>1332</v>
       </c>
-      <c r="E412" t="s">
+      <c r="E412" s="1" t="s">
         <v>1333</v>
       </c>
       <c r="F412" t="s">
@@ -24061,7 +24017,7 @@
       <c r="D413" t="s">
         <v>1335</v>
       </c>
-      <c r="E413" t="s">
+      <c r="E413" s="1" t="s">
         <v>1336</v>
       </c>
       <c r="F413" t="s">
@@ -24102,7 +24058,7 @@
       <c r="D414" t="s">
         <v>1337</v>
       </c>
-      <c r="E414" t="s">
+      <c r="E414" s="1" t="s">
         <v>1338</v>
       </c>
       <c r="F414" t="s">
@@ -24143,7 +24099,7 @@
       <c r="D415" t="s">
         <v>1341</v>
       </c>
-      <c r="E415" t="s">
+      <c r="E415" s="1" t="s">
         <v>1342</v>
       </c>
       <c r="F415" t="s">
@@ -24184,7 +24140,7 @@
       <c r="D416" t="s">
         <v>1344</v>
       </c>
-      <c r="E416" t="s">
+      <c r="E416" s="1" t="s">
         <v>1345</v>
       </c>
       <c r="F416" t="s">
@@ -24225,7 +24181,7 @@
       <c r="D417" t="s">
         <v>1348</v>
       </c>
-      <c r="E417" t="s">
+      <c r="E417" s="1" t="s">
         <v>1349</v>
       </c>
       <c r="F417" t="s">
@@ -24266,7 +24222,7 @@
       <c r="D418" t="s">
         <v>1352</v>
       </c>
-      <c r="E418" t="s">
+      <c r="E418" s="1" t="s">
         <v>1353</v>
       </c>
       <c r="F418" t="s">
@@ -24307,7 +24263,7 @@
       <c r="D419" t="s">
         <v>1355</v>
       </c>
-      <c r="E419" t="s">
+      <c r="E419" s="1" t="s">
         <v>1356</v>
       </c>
       <c r="F419" t="s">
@@ -24348,7 +24304,7 @@
       <c r="D420" t="s">
         <v>1357</v>
       </c>
-      <c r="E420" t="s">
+      <c r="E420" s="1" t="s">
         <v>1358</v>
       </c>
       <c r="F420" t="s">
@@ -24389,7 +24345,7 @@
       <c r="D421" t="s">
         <v>1361</v>
       </c>
-      <c r="E421" t="s">
+      <c r="E421" s="1" t="s">
         <v>1362</v>
       </c>
       <c r="F421" t="s">
@@ -24430,7 +24386,7 @@
       <c r="D422" t="s">
         <v>1364</v>
       </c>
-      <c r="E422" t="s">
+      <c r="E422" s="1" t="s">
         <v>1365</v>
       </c>
       <c r="F422" t="s">
@@ -24471,7 +24427,7 @@
       <c r="D423" t="s">
         <v>1309</v>
       </c>
-      <c r="E423" t="s">
+      <c r="E423" s="1" t="s">
         <v>1366</v>
       </c>
       <c r="F423" t="s">
@@ -24512,7 +24468,7 @@
       <c r="D424" t="s">
         <v>1369</v>
       </c>
-      <c r="E424" t="s">
+      <c r="E424" s="1" t="s">
         <v>1370</v>
       </c>
       <c r="F424" t="s">
@@ -24553,7 +24509,7 @@
       <c r="D425" t="s">
         <v>1372</v>
       </c>
-      <c r="E425" t="s">
+      <c r="E425" s="1" t="s">
         <v>1373</v>
       </c>
       <c r="F425" t="s">
@@ -24594,7 +24550,7 @@
       <c r="D426" t="s">
         <v>1377</v>
       </c>
-      <c r="E426" t="s">
+      <c r="E426" s="1" t="s">
         <v>1378</v>
       </c>
       <c r="F426" t="s">
@@ -24635,7 +24591,7 @@
       <c r="D427" t="s">
         <v>1380</v>
       </c>
-      <c r="E427" t="s">
+      <c r="E427" s="1" t="s">
         <v>1381</v>
       </c>
       <c r="F427" t="s">
@@ -24676,7 +24632,7 @@
       <c r="D428" t="s">
         <v>1383</v>
       </c>
-      <c r="E428" t="s">
+      <c r="E428" s="1" t="s">
         <v>1384</v>
       </c>
       <c r="F428" t="s">
@@ -24717,7 +24673,7 @@
       <c r="D429" t="s">
         <v>1385</v>
       </c>
-      <c r="E429" t="s">
+      <c r="E429" s="1" t="s">
         <v>1386</v>
       </c>
       <c r="F429" t="s">
@@ -24758,7 +24714,7 @@
       <c r="D430" t="s">
         <v>1388</v>
       </c>
-      <c r="E430" t="s">
+      <c r="E430" s="1" t="s">
         <v>1389</v>
       </c>
       <c r="F430" t="s">
@@ -24799,7 +24755,7 @@
       <c r="D431" t="s">
         <v>1309</v>
       </c>
-      <c r="E431" t="s">
+      <c r="E431" s="1" t="s">
         <v>1391</v>
       </c>
       <c r="F431" t="s">
@@ -24840,7 +24796,7 @@
       <c r="D432" t="s">
         <v>1393</v>
       </c>
-      <c r="E432" t="s">
+      <c r="E432" s="1" t="s">
         <v>1394</v>
       </c>
       <c r="F432" t="s">
@@ -24881,7 +24837,7 @@
       <c r="D433" t="s">
         <v>1396</v>
       </c>
-      <c r="E433" t="s">
+      <c r="E433" s="1" t="s">
         <v>1397</v>
       </c>
       <c r="F433" t="s">
@@ -24922,7 +24878,7 @@
       <c r="D434" t="s">
         <v>1398</v>
       </c>
-      <c r="E434" t="s">
+      <c r="E434" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F434" t="s">
@@ -24963,7 +24919,7 @@
       <c r="D435" t="s">
         <v>1093</v>
       </c>
-      <c r="E435" t="s">
+      <c r="E435" s="1" t="s">
         <v>1157</v>
       </c>
       <c r="F435" t="s">
@@ -25004,7 +24960,7 @@
       <c r="D436" t="s">
         <v>1401</v>
       </c>
-      <c r="E436" t="s">
+      <c r="E436" s="1" t="s">
         <v>1402</v>
       </c>
       <c r="F436" t="s">
@@ -25045,7 +25001,7 @@
       <c r="D437" t="s">
         <v>1404</v>
       </c>
-      <c r="E437" t="s">
+      <c r="E437" s="1" t="s">
         <v>1405</v>
       </c>
       <c r="F437" t="s">
@@ -25086,7 +25042,7 @@
       <c r="D438" t="s">
         <v>1407</v>
       </c>
-      <c r="E438" t="s">
+      <c r="E438" s="1" t="s">
         <v>1408</v>
       </c>
       <c r="F438" t="s">
@@ -25127,7 +25083,7 @@
       <c r="D439" t="s">
         <v>1411</v>
       </c>
-      <c r="E439" t="s">
+      <c r="E439" s="1" t="s">
         <v>1412</v>
       </c>
       <c r="F439" t="s">
@@ -25168,7 +25124,7 @@
       <c r="D440" t="s">
         <v>1309</v>
       </c>
-      <c r="E440" t="s">
+      <c r="E440" s="1" t="s">
         <v>1413</v>
       </c>
       <c r="F440" t="s">
@@ -25209,7 +25165,7 @@
       <c r="D441" t="s">
         <v>1416</v>
       </c>
-      <c r="E441" t="s">
+      <c r="E441" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F441" t="s">
@@ -25250,7 +25206,7 @@
       <c r="D442" t="s">
         <v>1419</v>
       </c>
-      <c r="E442" t="s">
+      <c r="E442" s="1" t="s">
         <v>1298</v>
       </c>
       <c r="F442" t="s">
@@ -25291,7 +25247,7 @@
       <c r="D443" t="s">
         <v>1420</v>
       </c>
-      <c r="E443" t="s">
+      <c r="E443" s="1" t="s">
         <v>482</v>
       </c>
       <c r="F443" t="s">
@@ -25332,7 +25288,7 @@
       <c r="D444" t="s">
         <v>1423</v>
       </c>
-      <c r="E444" t="s">
+      <c r="E444" s="1" t="s">
         <v>1424</v>
       </c>
       <c r="F444" t="s">
@@ -25373,7 +25329,7 @@
       <c r="D445" t="s">
         <v>1425</v>
       </c>
-      <c r="E445" t="s">
+      <c r="E445" s="1" t="s">
         <v>1426</v>
       </c>
       <c r="F445" t="s">
@@ -25414,7 +25370,7 @@
       <c r="D446" t="s">
         <v>1309</v>
       </c>
-      <c r="E446" t="s">
+      <c r="E446" s="1" t="s">
         <v>1428</v>
       </c>
       <c r="F446" t="s">
@@ -25455,7 +25411,7 @@
       <c r="D447" t="s">
         <v>1429</v>
       </c>
-      <c r="E447" t="s">
+      <c r="E447" s="1" t="s">
         <v>1430</v>
       </c>
       <c r="F447" t="s">
@@ -25496,7 +25452,7 @@
       <c r="D448" t="s">
         <v>1432</v>
       </c>
-      <c r="E448" t="s">
+      <c r="E448" s="1" t="s">
         <v>1433</v>
       </c>
       <c r="F448" t="s">
@@ -25537,7 +25493,7 @@
       <c r="D449" t="s">
         <v>1435</v>
       </c>
-      <c r="E449" t="s">
+      <c r="E449" s="1" t="s">
         <v>1436</v>
       </c>
       <c r="F449" t="s">
@@ -25578,7 +25534,7 @@
       <c r="D450" t="s">
         <v>1309</v>
       </c>
-      <c r="E450" t="s">
+      <c r="E450" s="1" t="s">
         <v>1438</v>
       </c>
       <c r="F450" t="s">
@@ -25619,7 +25575,7 @@
       <c r="D451" t="s">
         <v>1441</v>
       </c>
-      <c r="E451" t="s">
+      <c r="E451" s="1" t="s">
         <v>1442</v>
       </c>
       <c r="F451" t="s">
@@ -25660,7 +25616,7 @@
       <c r="D452" t="s">
         <v>1444</v>
       </c>
-      <c r="E452" t="s">
+      <c r="E452" s="1" t="s">
         <v>1445</v>
       </c>
       <c r="F452" t="s">
@@ -25701,7 +25657,7 @@
       <c r="D453" t="s">
         <v>1447</v>
       </c>
-      <c r="E453" t="s">
+      <c r="E453" s="1" t="s">
         <v>110</v>
       </c>
       <c r="F453" t="s">
@@ -25742,7 +25698,7 @@
       <c r="D454" t="s">
         <v>1450</v>
       </c>
-      <c r="E454" t="s">
+      <c r="E454" s="1" t="s">
         <v>1451</v>
       </c>
       <c r="F454" t="s">
@@ -25783,7 +25739,7 @@
       <c r="D455" t="s">
         <v>1454</v>
       </c>
-      <c r="E455" t="s">
+      <c r="E455" s="1" t="s">
         <v>1455</v>
       </c>
       <c r="F455" t="s">
@@ -25824,7 +25780,7 @@
       <c r="D456" t="s">
         <v>1458</v>
       </c>
-      <c r="E456" t="s">
+      <c r="E456" s="1" t="s">
         <v>1459</v>
       </c>
       <c r="F456" t="s">
@@ -25865,7 +25821,7 @@
       <c r="D457" t="s">
         <v>1462</v>
       </c>
-      <c r="E457" t="s">
+      <c r="E457" s="1" t="s">
         <v>1463</v>
       </c>
       <c r="F457" t="s">
@@ -25906,7 +25862,7 @@
       <c r="D458" t="s">
         <v>1465</v>
       </c>
-      <c r="E458" t="s">
+      <c r="E458" s="1" t="s">
         <v>1466</v>
       </c>
       <c r="F458" t="s">
@@ -25947,7 +25903,7 @@
       <c r="D459" t="s">
         <v>1468</v>
       </c>
-      <c r="E459" t="s">
+      <c r="E459" s="1" t="s">
         <v>1469</v>
       </c>
       <c r="F459" t="s">
@@ -25988,7 +25944,7 @@
       <c r="D460" t="s">
         <v>1472</v>
       </c>
-      <c r="E460" t="s">
+      <c r="E460" s="1" t="s">
         <v>1473</v>
       </c>
       <c r="F460" t="s">
@@ -26029,7 +25985,7 @@
       <c r="D461" t="s">
         <v>1475</v>
       </c>
-      <c r="E461" t="s">
+      <c r="E461" s="1" t="s">
         <v>1476</v>
       </c>
       <c r="F461" t="s">
@@ -26070,7 +26026,7 @@
       <c r="D462" t="s">
         <v>1479</v>
       </c>
-      <c r="E462" t="s">
+      <c r="E462" s="1" t="s">
         <v>1480</v>
       </c>
       <c r="F462" t="s">
@@ -26111,7 +26067,7 @@
       <c r="D463" t="s">
         <v>1481</v>
       </c>
-      <c r="E463" t="s">
+      <c r="E463" s="1" t="s">
         <v>1482</v>
       </c>
       <c r="F463" t="s">
@@ -26152,7 +26108,7 @@
       <c r="D464" t="s">
         <v>1309</v>
       </c>
-      <c r="E464" t="s">
+      <c r="E464" s="1" t="s">
         <v>1484</v>
       </c>
       <c r="F464" t="s">
@@ -26193,7 +26149,7 @@
       <c r="D465" t="s">
         <v>1486</v>
       </c>
-      <c r="E465" t="s">
+      <c r="E465" s="1" t="s">
         <v>1487</v>
       </c>
       <c r="F465" t="s">
@@ -26234,7 +26190,7 @@
       <c r="D466" t="s">
         <v>1489</v>
       </c>
-      <c r="E466" t="s">
+      <c r="E466" s="1" t="s">
         <v>1490</v>
       </c>
       <c r="F466" t="s">
@@ -26275,7 +26231,7 @@
       <c r="D467" t="s">
         <v>1492</v>
       </c>
-      <c r="E467" t="s">
+      <c r="E467" s="1" t="s">
         <v>1493</v>
       </c>
       <c r="F467" t="s">
@@ -26316,7 +26272,7 @@
       <c r="D468" t="s">
         <v>1496</v>
       </c>
-      <c r="E468" t="s">
+      <c r="E468" s="1" t="s">
         <v>1497</v>
       </c>
       <c r="F468" t="s">
@@ -26357,7 +26313,7 @@
       <c r="D469" t="s">
         <v>1500</v>
       </c>
-      <c r="E469" t="s">
+      <c r="E469" s="1" t="s">
         <v>1426</v>
       </c>
       <c r="F469" t="s">
@@ -26398,7 +26354,7 @@
       <c r="D470" t="s">
         <v>1503</v>
       </c>
-      <c r="E470" t="s">
+      <c r="E470" s="1" t="s">
         <v>1504</v>
       </c>
       <c r="F470" t="s">
@@ -26439,7 +26395,7 @@
       <c r="D471" t="s">
         <v>1507</v>
       </c>
-      <c r="E471" t="s">
+      <c r="E471" s="1" t="s">
         <v>1508</v>
       </c>
       <c r="F471" t="s">
@@ -26480,7 +26436,7 @@
       <c r="D472" t="s">
         <v>1511</v>
       </c>
-      <c r="E472" t="s">
+      <c r="E472" s="1" t="s">
         <v>274</v>
       </c>
       <c r="F472" t="s">
@@ -26521,7 +26477,7 @@
       <c r="D473" t="s">
         <v>1514</v>
       </c>
-      <c r="E473" t="s">
+      <c r="E473" s="1" t="s">
         <v>1515</v>
       </c>
       <c r="F473" t="s">
@@ -26562,7 +26518,7 @@
       <c r="D474" t="s">
         <v>1517</v>
       </c>
-      <c r="E474" t="s">
+      <c r="E474" s="1" t="s">
         <v>1518</v>
       </c>
       <c r="F474" t="s">
@@ -26603,7 +26559,7 @@
       <c r="D475" t="s">
         <v>1519</v>
       </c>
-      <c r="E475" t="s">
+      <c r="E475" s="1" t="s">
         <v>1520</v>
       </c>
       <c r="F475" t="s">
@@ -26644,7 +26600,7 @@
       <c r="D476" t="s">
         <v>1309</v>
       </c>
-      <c r="E476" t="s">
+      <c r="E476" s="1" t="s">
         <v>1522</v>
       </c>
       <c r="F476" t="s">
@@ -26685,7 +26641,7 @@
       <c r="D477" t="s">
         <v>1523</v>
       </c>
-      <c r="E477" t="s">
+      <c r="E477" s="1" t="s">
         <v>1524</v>
       </c>
       <c r="F477" t="s">
@@ -26726,7 +26682,7 @@
       <c r="D478" t="s">
         <v>1526</v>
       </c>
-      <c r="E478" t="s">
+      <c r="E478" s="1" t="s">
         <v>1527</v>
       </c>
       <c r="F478" t="s">
@@ -26767,7 +26723,7 @@
       <c r="D479" t="s">
         <v>1529</v>
       </c>
-      <c r="E479" t="s">
+      <c r="E479" s="1" t="s">
         <v>1530</v>
       </c>
       <c r="F479" t="s">
@@ -26808,7 +26764,7 @@
       <c r="D480" t="s">
         <v>1533</v>
       </c>
-      <c r="E480" t="s">
+      <c r="E480" s="1" t="s">
         <v>1534</v>
       </c>
       <c r="F480" t="s">
@@ -26849,7 +26805,7 @@
       <c r="D481" t="s">
         <v>1537</v>
       </c>
-      <c r="E481" t="s">
+      <c r="E481" s="1" t="s">
         <v>1538</v>
       </c>
       <c r="F481" t="s">
@@ -26890,7 +26846,7 @@
       <c r="D482" t="s">
         <v>1540</v>
       </c>
-      <c r="E482" t="s">
+      <c r="E482" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F482" t="s">
@@ -26931,7 +26887,7 @@
       <c r="D483" t="s">
         <v>1543</v>
       </c>
-      <c r="E483" t="s">
+      <c r="E483" s="1" t="s">
         <v>1544</v>
       </c>
       <c r="F483" t="s">
@@ -26972,7 +26928,7 @@
       <c r="D484" t="s">
         <v>1546</v>
       </c>
-      <c r="E484" t="s">
+      <c r="E484" s="1" t="s">
         <v>1547</v>
       </c>
       <c r="F484" t="s">
@@ -27013,7 +26969,7 @@
       <c r="D485" t="s">
         <v>1550</v>
       </c>
-      <c r="E485" t="s">
+      <c r="E485" s="1" t="s">
         <v>1551</v>
       </c>
       <c r="F485" t="s">
@@ -27054,7 +27010,7 @@
       <c r="D486" t="s">
         <v>1554</v>
       </c>
-      <c r="E486" t="s">
+      <c r="E486" s="1" t="s">
         <v>1555</v>
       </c>
       <c r="F486" t="s">
@@ -27095,7 +27051,7 @@
       <c r="D487" t="s">
         <v>1557</v>
       </c>
-      <c r="E487" t="s">
+      <c r="E487" s="1" t="s">
         <v>1558</v>
       </c>
       <c r="F487" t="s">
@@ -27136,7 +27092,7 @@
       <c r="D488" t="s">
         <v>1559</v>
       </c>
-      <c r="E488" t="s">
+      <c r="E488" s="1" t="s">
         <v>1560</v>
       </c>
       <c r="F488" t="s">
@@ -27177,7 +27133,7 @@
       <c r="D489" t="s">
         <v>1563</v>
       </c>
-      <c r="E489" t="s">
+      <c r="E489" s="1" t="s">
         <v>1564</v>
       </c>
       <c r="F489" t="s">
@@ -27218,7 +27174,7 @@
       <c r="D490" t="s">
         <v>1566</v>
       </c>
-      <c r="E490" t="s">
+      <c r="E490" s="1" t="s">
         <v>1567</v>
       </c>
       <c r="F490" t="s">
@@ -27259,7 +27215,7 @@
       <c r="D491" t="s">
         <v>1570</v>
       </c>
-      <c r="E491" t="s">
+      <c r="E491" s="1" t="s">
         <v>1571</v>
       </c>
       <c r="F491" t="s">
@@ -27300,7 +27256,7 @@
       <c r="D492" t="s">
         <v>1309</v>
       </c>
-      <c r="E492" t="s">
+      <c r="E492" s="1" t="s">
         <v>1573</v>
       </c>
       <c r="F492" t="s">
@@ -27341,7 +27297,7 @@
       <c r="D493" t="s">
         <v>1575</v>
       </c>
-      <c r="E493" t="s">
+      <c r="E493" s="1" t="s">
         <v>1576</v>
       </c>
       <c r="F493" t="s">
@@ -27382,7 +27338,7 @@
       <c r="D494" t="s">
         <v>1577</v>
       </c>
-      <c r="E494" t="s">
+      <c r="E494" s="1" t="s">
         <v>784</v>
       </c>
       <c r="F494" t="s">
@@ -27423,7 +27379,7 @@
       <c r="D495" t="s">
         <v>1579</v>
       </c>
-      <c r="E495" t="s">
+      <c r="E495" s="1" t="s">
         <v>1580</v>
       </c>
       <c r="F495" t="s">
@@ -27464,7 +27420,7 @@
       <c r="D496" t="s">
         <v>1540</v>
       </c>
-      <c r="E496" t="s">
+      <c r="E496" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F496" t="s">
@@ -27505,7 +27461,7 @@
       <c r="D497" t="s">
         <v>1581</v>
       </c>
-      <c r="E497" t="s">
+      <c r="E497" s="1" t="s">
         <v>1582</v>
       </c>
       <c r="F497" t="s">
@@ -27546,7 +27502,7 @@
       <c r="D498" t="s">
         <v>1584</v>
       </c>
-      <c r="E498" t="s">
+      <c r="E498" s="1" t="s">
         <v>1520</v>
       </c>
       <c r="F498" t="s">
@@ -27587,7 +27543,7 @@
       <c r="D499" t="s">
         <v>1309</v>
       </c>
-      <c r="E499" t="s">
+      <c r="E499" s="1" t="s">
         <v>1586</v>
       </c>
       <c r="F499" t="s">
@@ -27628,7 +27584,7 @@
       <c r="D500" t="s">
         <v>1589</v>
       </c>
-      <c r="E500" t="s">
+      <c r="E500" s="1" t="s">
         <v>1590</v>
       </c>
       <c r="F500" t="s">
@@ -27669,7 +27625,7 @@
       <c r="D501" t="s">
         <v>1593</v>
       </c>
-      <c r="E501" t="s">
+      <c r="E501" s="1" t="s">
         <v>1594</v>
       </c>
       <c r="F501" t="s">
@@ -27710,7 +27666,7 @@
       <c r="D502" t="s">
         <v>1595</v>
       </c>
-      <c r="E502" t="s">
+      <c r="E502" s="1" t="s">
         <v>1596</v>
       </c>
       <c r="F502" t="s">
@@ -27751,7 +27707,7 @@
       <c r="D503" t="s">
         <v>1598</v>
       </c>
-      <c r="E503" t="s">
+      <c r="E503" s="1" t="s">
         <v>1599</v>
       </c>
       <c r="F503" t="s">
@@ -27792,7 +27748,7 @@
       <c r="D504" t="s">
         <v>1468</v>
       </c>
-      <c r="E504" t="s">
+      <c r="E504" s="1" t="s">
         <v>1602</v>
       </c>
       <c r="F504" t="s">
@@ -27833,7 +27789,7 @@
       <c r="D505" t="s">
         <v>1486</v>
       </c>
-      <c r="E505" t="s">
+      <c r="E505" s="1" t="s">
         <v>1604</v>
       </c>
       <c r="F505" t="s">
@@ -27874,7 +27830,7 @@
       <c r="D506" t="s">
         <v>1605</v>
       </c>
-      <c r="E506" t="s">
+      <c r="E506" s="1" t="s">
         <v>1606</v>
       </c>
       <c r="F506" t="s">
@@ -27915,7 +27871,7 @@
       <c r="D507" t="s">
         <v>1608</v>
       </c>
-      <c r="E507" t="s">
+      <c r="E507" s="1" t="s">
         <v>1609</v>
       </c>
       <c r="F507" t="s">
@@ -27956,7 +27912,7 @@
       <c r="D508" t="s">
         <v>1540</v>
       </c>
-      <c r="E508" t="s">
+      <c r="E508" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F508" t="s">
@@ -27997,7 +27953,7 @@
       <c r="D509" t="s">
         <v>1613</v>
       </c>
-      <c r="E509" t="s">
+      <c r="E509" s="1" t="s">
         <v>1614</v>
       </c>
       <c r="F509" t="s">
@@ -28038,7 +27994,7 @@
       <c r="D510" t="s">
         <v>1616</v>
       </c>
-      <c r="E510" t="s">
+      <c r="E510" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F510" t="s">
@@ -28079,7 +28035,7 @@
       <c r="D511" t="s">
         <v>1618</v>
       </c>
-      <c r="E511" t="s">
+      <c r="E511" s="1" t="s">
         <v>1619</v>
       </c>
       <c r="F511" t="s">
@@ -28120,7 +28076,7 @@
       <c r="D512" t="s">
         <v>1621</v>
       </c>
-      <c r="E512" t="s">
+      <c r="E512" s="1" t="s">
         <v>1622</v>
       </c>
       <c r="F512" t="s">
@@ -28161,7 +28117,7 @@
       <c r="D513" t="s">
         <v>1624</v>
       </c>
-      <c r="E513" t="s">
+      <c r="E513" s="1" t="s">
         <v>1625</v>
       </c>
       <c r="F513" t="s">
@@ -28202,7 +28158,7 @@
       <c r="D514" t="s">
         <v>1309</v>
       </c>
-      <c r="E514" t="s">
+      <c r="E514" s="1" t="s">
         <v>1626</v>
       </c>
       <c r="F514" t="s">
@@ -28243,7 +28199,7 @@
       <c r="D515" t="s">
         <v>1540</v>
       </c>
-      <c r="E515" t="s">
+      <c r="E515" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F515" t="s">
@@ -28284,7 +28240,7 @@
       <c r="D516" t="s">
         <v>1627</v>
       </c>
-      <c r="E516" t="s">
+      <c r="E516" s="1" t="s">
         <v>1628</v>
       </c>
       <c r="F516" t="s">
@@ -28325,7 +28281,7 @@
       <c r="D517" t="s">
         <v>1629</v>
       </c>
-      <c r="E517" t="s">
+      <c r="E517" s="1" t="s">
         <v>1630</v>
       </c>
       <c r="F517" t="s">
@@ -28366,7 +28322,7 @@
       <c r="D518" t="s">
         <v>1632</v>
       </c>
-      <c r="E518" t="s">
+      <c r="E518" s="1" t="s">
         <v>1633</v>
       </c>
       <c r="F518" t="s">
@@ -28407,7 +28363,7 @@
       <c r="D519" t="s">
         <v>1635</v>
       </c>
-      <c r="E519" t="s">
+      <c r="E519" s="1" t="s">
         <v>1636</v>
       </c>
       <c r="F519" t="s">
@@ -28448,7 +28404,7 @@
       <c r="D520" t="s">
         <v>1639</v>
       </c>
-      <c r="E520" t="s">
+      <c r="E520" s="1" t="s">
         <v>1640</v>
       </c>
       <c r="F520" t="s">
@@ -28489,7 +28445,7 @@
       <c r="D521" t="s">
         <v>1309</v>
       </c>
-      <c r="E521" t="s">
+      <c r="E521" s="1" t="s">
         <v>1641</v>
       </c>
       <c r="F521" t="s">
@@ -28530,7 +28486,7 @@
       <c r="D522" t="s">
         <v>1644</v>
       </c>
-      <c r="E522" t="s">
+      <c r="E522" s="1" t="s">
         <v>1645</v>
       </c>
       <c r="F522" t="s">
@@ -28571,7 +28527,7 @@
       <c r="D523" t="s">
         <v>1648</v>
       </c>
-      <c r="E523" t="s">
+      <c r="E523" s="1" t="s">
         <v>1649</v>
       </c>
       <c r="F523" t="s">
@@ -28612,7 +28568,7 @@
       <c r="D524" t="s">
         <v>1650</v>
       </c>
-      <c r="E524" t="s">
+      <c r="E524" s="1" t="s">
         <v>1651</v>
       </c>
       <c r="F524" t="s">
@@ -28653,7 +28609,7 @@
       <c r="D525" t="s">
         <v>1653</v>
       </c>
-      <c r="E525" t="s">
+      <c r="E525" s="1" t="s">
         <v>1534</v>
       </c>
       <c r="F525" t="s">
@@ -28694,7 +28650,7 @@
       <c r="D526" t="s">
         <v>1655</v>
       </c>
-      <c r="E526" t="s">
+      <c r="E526" s="1" t="s">
         <v>1656</v>
       </c>
       <c r="F526" t="s">
@@ -28735,7 +28691,7 @@
       <c r="D527" t="s">
         <v>1657</v>
       </c>
-      <c r="E527" t="s">
+      <c r="E527" s="1" t="s">
         <v>1658</v>
       </c>
       <c r="F527" t="s">
@@ -28776,7 +28732,7 @@
       <c r="D528" t="s">
         <v>1659</v>
       </c>
-      <c r="E528" t="s">
+      <c r="E528" s="1" t="s">
         <v>1660</v>
       </c>
       <c r="F528" t="s">
@@ -28817,7 +28773,7 @@
       <c r="D529" t="s">
         <v>1309</v>
       </c>
-      <c r="E529" t="s">
+      <c r="E529" s="1" t="s">
         <v>1661</v>
       </c>
       <c r="F529" t="s">
@@ -28858,7 +28814,7 @@
       <c r="D530" t="s">
         <v>1664</v>
       </c>
-      <c r="E530" t="s">
+      <c r="E530" s="1" t="s">
         <v>1665</v>
       </c>
       <c r="F530" t="s">
@@ -28899,7 +28855,7 @@
       <c r="D531" t="s">
         <v>1581</v>
       </c>
-      <c r="E531" t="s">
+      <c r="E531" s="1" t="s">
         <v>1582</v>
       </c>
       <c r="F531" t="s">
@@ -28940,7 +28896,7 @@
       <c r="D532" t="s">
         <v>1669</v>
       </c>
-      <c r="E532" t="s">
+      <c r="E532" s="1" t="s">
         <v>733</v>
       </c>
       <c r="F532" t="s">
@@ -28981,7 +28937,7 @@
       <c r="D533" t="s">
         <v>1671</v>
       </c>
-      <c r="E533" t="s">
+      <c r="E533" s="1" t="s">
         <v>1672</v>
       </c>
       <c r="F533" t="s">
@@ -29022,7 +28978,7 @@
       <c r="D534" t="s">
         <v>1675</v>
       </c>
-      <c r="E534" t="s">
+      <c r="E534" s="1" t="s">
         <v>1676</v>
       </c>
       <c r="F534" t="s">
@@ -29063,7 +29019,7 @@
       <c r="D535" t="s">
         <v>1679</v>
       </c>
-      <c r="E535" t="s">
+      <c r="E535" s="1" t="s">
         <v>1680</v>
       </c>
       <c r="F535" t="s">
@@ -29104,7 +29060,7 @@
       <c r="D536" t="s">
         <v>1683</v>
       </c>
-      <c r="E536" t="s">
+      <c r="E536" s="1" t="s">
         <v>1684</v>
       </c>
       <c r="F536" t="s">
@@ -29145,7 +29101,7 @@
       <c r="D537" t="s">
         <v>1309</v>
       </c>
-      <c r="E537" t="s">
+      <c r="E537" s="1" t="s">
         <v>1686</v>
       </c>
       <c r="F537" t="s">
@@ -29186,7 +29142,7 @@
       <c r="D538" t="s">
         <v>1688</v>
       </c>
-      <c r="E538" t="s">
+      <c r="E538" s="1" t="s">
         <v>1689</v>
       </c>
       <c r="F538" t="s">
@@ -29227,7 +29183,7 @@
       <c r="D539" t="s">
         <v>1653</v>
       </c>
-      <c r="E539" t="s">
+      <c r="E539" s="1" t="s">
         <v>974</v>
       </c>
       <c r="F539" t="s">
@@ -29268,7 +29224,7 @@
       <c r="D540" t="s">
         <v>1693</v>
       </c>
-      <c r="E540" t="s">
+      <c r="E540" s="1" t="s">
         <v>1694</v>
       </c>
       <c r="F540" t="s">
@@ -29309,7 +29265,7 @@
       <c r="D541" t="s">
         <v>1697</v>
       </c>
-      <c r="E541" t="s">
+      <c r="E541" s="1" t="s">
         <v>1698</v>
       </c>
       <c r="F541" t="s">
@@ -29350,7 +29306,7 @@
       <c r="D542" t="s">
         <v>1581</v>
       </c>
-      <c r="E542" t="s">
+      <c r="E542" s="1" t="s">
         <v>1700</v>
       </c>
       <c r="F542" t="s">
@@ -29391,7 +29347,7 @@
       <c r="D543" t="s">
         <v>1701</v>
       </c>
-      <c r="E543" t="s">
+      <c r="E543" s="1" t="s">
         <v>1702</v>
       </c>
       <c r="F543" t="s">
@@ -29432,7 +29388,7 @@
       <c r="D544" t="s">
         <v>1704</v>
       </c>
-      <c r="E544" t="s">
+      <c r="E544" s="1" t="s">
         <v>1705</v>
       </c>
       <c r="F544" t="s">
@@ -29473,7 +29429,7 @@
       <c r="D545" t="s">
         <v>1309</v>
       </c>
-      <c r="E545" t="s">
+      <c r="E545" s="1" t="s">
         <v>1707</v>
       </c>
       <c r="F545" t="s">
@@ -29514,7 +29470,7 @@
       <c r="D546" t="s">
         <v>1709</v>
       </c>
-      <c r="E546" t="s">
+      <c r="E546" s="1" t="s">
         <v>1710</v>
       </c>
       <c r="F546" t="s">
@@ -29555,7 +29511,7 @@
       <c r="D547" t="s">
         <v>1712</v>
       </c>
-      <c r="E547" t="s">
+      <c r="E547" s="1" t="s">
         <v>1713</v>
       </c>
       <c r="F547" t="s">
@@ -29596,7 +29552,7 @@
       <c r="D548" t="s">
         <v>1715</v>
       </c>
-      <c r="E548" t="s">
+      <c r="E548" s="1" t="s">
         <v>1716</v>
       </c>
       <c r="F548" t="s">
@@ -29637,7 +29593,7 @@
       <c r="D549" t="s">
         <v>1719</v>
       </c>
-      <c r="E549" t="s">
+      <c r="E549" s="1" t="s">
         <v>1720</v>
       </c>
       <c r="F549" t="s">
@@ -29678,7 +29634,7 @@
       <c r="D550" t="s">
         <v>1722</v>
       </c>
-      <c r="E550" t="s">
+      <c r="E550" s="1" t="s">
         <v>1723</v>
       </c>
       <c r="F550" t="s">
@@ -29719,7 +29675,7 @@
       <c r="D551" t="s">
         <v>1540</v>
       </c>
-      <c r="E551" t="s">
+      <c r="E551" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F551" t="s">
@@ -29760,7 +29716,7 @@
       <c r="D552" t="s">
         <v>1540</v>
       </c>
-      <c r="E552" t="s">
+      <c r="E552" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F552" t="s">
@@ -29801,7 +29757,7 @@
       <c r="D553" t="s">
         <v>1581</v>
       </c>
-      <c r="E553" t="s">
+      <c r="E553" s="1" t="s">
         <v>1582</v>
       </c>
       <c r="F553" t="s">
@@ -29842,7 +29798,7 @@
       <c r="D554" t="s">
         <v>1725</v>
       </c>
-      <c r="E554" t="s">
+      <c r="E554" s="1" t="s">
         <v>1726</v>
       </c>
       <c r="F554" t="s">
@@ -29883,7 +29839,7 @@
       <c r="D555" t="s">
         <v>1729</v>
       </c>
-      <c r="E555" t="s">
+      <c r="E555" s="1" t="s">
         <v>1730</v>
       </c>
       <c r="F555" t="s">
@@ -29924,7 +29880,7 @@
       <c r="D556" t="s">
         <v>1733</v>
       </c>
-      <c r="E556" t="s">
+      <c r="E556" s="1" t="s">
         <v>1734</v>
       </c>
       <c r="F556" t="s">
@@ -29965,7 +29921,7 @@
       <c r="D557" t="s">
         <v>1737</v>
       </c>
-      <c r="E557" t="s">
+      <c r="E557" s="1" t="s">
         <v>1738</v>
       </c>
       <c r="F557" t="s">
@@ -30006,7 +29962,7 @@
       <c r="D558" t="s">
         <v>1581</v>
       </c>
-      <c r="E558" t="s">
+      <c r="E558" s="1" t="s">
         <v>1739</v>
       </c>
       <c r="F558" t="s">
@@ -30047,7 +30003,7 @@
       <c r="D559" t="s">
         <v>1444</v>
       </c>
-      <c r="E559" t="s">
+      <c r="E559" s="1" t="s">
         <v>1741</v>
       </c>
       <c r="F559" t="s">
@@ -30088,7 +30044,7 @@
       <c r="D560" t="s">
         <v>1742</v>
       </c>
-      <c r="E560" t="s">
+      <c r="E560" s="1" t="s">
         <v>1743</v>
       </c>
       <c r="F560" t="s">
@@ -30129,7 +30085,7 @@
       <c r="D561" t="s">
         <v>1746</v>
       </c>
-      <c r="E561" t="s">
+      <c r="E561" s="1" t="s">
         <v>1747</v>
       </c>
       <c r="F561" t="s">
@@ -30170,7 +30126,7 @@
       <c r="D562" t="s">
         <v>1750</v>
       </c>
-      <c r="E562" t="s">
+      <c r="E562" s="1" t="s">
         <v>1751</v>
       </c>
       <c r="F562" t="s">
@@ -30211,7 +30167,7 @@
       <c r="D563" t="s">
         <v>1753</v>
       </c>
-      <c r="E563" t="s">
+      <c r="E563" s="1" t="s">
         <v>1754</v>
       </c>
       <c r="F563" t="s">
@@ -30252,7 +30208,7 @@
       <c r="D564" t="s">
         <v>1755</v>
       </c>
-      <c r="E564" t="s">
+      <c r="E564" s="1" t="s">
         <v>1756</v>
       </c>
       <c r="F564" t="s">
@@ -30293,7 +30249,7 @@
       <c r="D565" t="s">
         <v>1758</v>
       </c>
-      <c r="E565" t="s">
+      <c r="E565" s="1" t="s">
         <v>1759</v>
       </c>
       <c r="F565" t="s">
@@ -30334,7 +30290,7 @@
       <c r="D566" t="s">
         <v>1761</v>
       </c>
-      <c r="E566" t="s">
+      <c r="E566" s="1" t="s">
         <v>1762</v>
       </c>
       <c r="F566" t="s">
@@ -30375,7 +30331,7 @@
       <c r="D567" t="s">
         <v>1765</v>
       </c>
-      <c r="E567" t="s">
+      <c r="E567" s="1" t="s">
         <v>1766</v>
       </c>
       <c r="F567" t="s">
@@ -30416,7 +30372,7 @@
       <c r="D568" t="s">
         <v>1768</v>
       </c>
-      <c r="E568" t="s">
+      <c r="E568" s="1" t="s">
         <v>1769</v>
       </c>
       <c r="F568" t="s">
@@ -30457,7 +30413,7 @@
       <c r="D569" t="s">
         <v>1771</v>
       </c>
-      <c r="E569" t="s">
+      <c r="E569" s="1" t="s">
         <v>1772</v>
       </c>
       <c r="F569" t="s">
@@ -30498,7 +30454,7 @@
       <c r="D570" t="s">
         <v>1540</v>
       </c>
-      <c r="E570" t="s">
+      <c r="E570" s="1" t="s">
         <v>1774</v>
       </c>
       <c r="F570" t="s">
@@ -30539,7 +30495,7 @@
       <c r="D571" t="s">
         <v>1581</v>
       </c>
-      <c r="E571" t="s">
+      <c r="E571" s="1" t="s">
         <v>1776</v>
       </c>
       <c r="F571" t="s">
@@ -30580,7 +30536,7 @@
       <c r="D572" t="s">
         <v>1779</v>
       </c>
-      <c r="E572" t="s">
+      <c r="E572" s="1" t="s">
         <v>1780</v>
       </c>
       <c r="F572" t="s">
@@ -30621,7 +30577,7 @@
       <c r="D573" t="s">
         <v>1781</v>
       </c>
-      <c r="E573" t="s">
+      <c r="E573" s="1" t="s">
         <v>1782</v>
       </c>
       <c r="F573" t="s">
@@ -30662,7 +30618,7 @@
       <c r="D574" t="s">
         <v>1554</v>
       </c>
-      <c r="E574" t="s">
+      <c r="E574" s="1" t="s">
         <v>1784</v>
       </c>
       <c r="F574" t="s">
@@ -30703,7 +30659,7 @@
       <c r="D575" t="s">
         <v>1786</v>
       </c>
-      <c r="E575" t="s">
+      <c r="E575" s="1" t="s">
         <v>1787</v>
       </c>
       <c r="F575" t="s">
@@ -30744,7 +30700,7 @@
       <c r="D576" t="s">
         <v>1789</v>
       </c>
-      <c r="E576" t="s">
+      <c r="E576" s="1" t="s">
         <v>1790</v>
       </c>
       <c r="F576" t="s">
@@ -30785,7 +30741,7 @@
       <c r="D577" t="s">
         <v>1792</v>
       </c>
-      <c r="E577" t="s">
+      <c r="E577" s="1" t="s">
         <v>1793</v>
       </c>
       <c r="F577" t="s">
@@ -30826,7 +30782,7 @@
       <c r="D578" t="s">
         <v>1796</v>
       </c>
-      <c r="E578" t="s">
+      <c r="E578" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F578" t="s">
@@ -30867,7 +30823,7 @@
       <c r="D579" t="s">
         <v>1798</v>
       </c>
-      <c r="E579" t="s">
+      <c r="E579" s="1" t="s">
         <v>1799</v>
       </c>
       <c r="F579" t="s">
@@ -30908,7 +30864,7 @@
       <c r="D580" t="s">
         <v>1801</v>
       </c>
-      <c r="E580" t="s">
+      <c r="E580" s="1" t="s">
         <v>1802</v>
       </c>
       <c r="F580" t="s">
@@ -30949,7 +30905,7 @@
       <c r="D581" t="s">
         <v>1803</v>
       </c>
-      <c r="E581" t="s">
+      <c r="E581" s="1" t="s">
         <v>1804</v>
       </c>
       <c r="F581" t="s">
@@ -30990,7 +30946,7 @@
       <c r="D582" t="s">
         <v>1805</v>
       </c>
-      <c r="E582" t="s">
+      <c r="E582" s="1" t="s">
         <v>1806</v>
       </c>
       <c r="F582" t="s">
@@ -31031,7 +30987,7 @@
       <c r="D583" t="s">
         <v>1808</v>
       </c>
-      <c r="E583" t="s">
+      <c r="E583" s="1" t="s">
         <v>1809</v>
       </c>
       <c r="F583" t="s">
@@ -31072,7 +31028,7 @@
       <c r="D584" t="s">
         <v>1581</v>
       </c>
-      <c r="E584" t="s">
+      <c r="E584" s="1" t="s">
         <v>1811</v>
       </c>
       <c r="F584" t="s">
@@ -31113,7 +31069,7 @@
       <c r="D585" t="s">
         <v>1812</v>
       </c>
-      <c r="E585" t="s">
+      <c r="E585" s="1" t="s">
         <v>1813</v>
       </c>
       <c r="F585" t="s">
@@ -31154,7 +31110,7 @@
       <c r="D586" t="s">
         <v>1815</v>
       </c>
-      <c r="E586" t="s">
+      <c r="E586" s="1" t="s">
         <v>1816</v>
       </c>
       <c r="F586" t="s">
@@ -31195,7 +31151,7 @@
       <c r="D587" t="s">
         <v>1817</v>
       </c>
-      <c r="E587" t="s">
+      <c r="E587" s="1" t="s">
         <v>1818</v>
       </c>
       <c r="F587" t="s">
@@ -31236,7 +31192,7 @@
       <c r="D588" t="s">
         <v>1486</v>
       </c>
-      <c r="E588" t="s">
+      <c r="E588" s="1" t="s">
         <v>1819</v>
       </c>
       <c r="F588" t="s">
@@ -31277,7 +31233,7 @@
       <c r="D589" t="s">
         <v>1820</v>
       </c>
-      <c r="E589" t="s">
+      <c r="E589" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F589" t="s">
@@ -31318,7 +31274,7 @@
       <c r="D590" t="s">
         <v>1822</v>
       </c>
-      <c r="E590" t="s">
+      <c r="E590" s="1" t="s">
         <v>1823</v>
       </c>
       <c r="F590" t="s">
@@ -31359,7 +31315,7 @@
       <c r="D591" t="s">
         <v>1824</v>
       </c>
-      <c r="E591" t="s">
+      <c r="E591" s="1" t="s">
         <v>1825</v>
       </c>
       <c r="F591" t="s">
@@ -31400,7 +31356,7 @@
       <c r="D592" t="s">
         <v>1827</v>
       </c>
-      <c r="E592" t="s">
+      <c r="E592" s="1" t="s">
         <v>1828</v>
       </c>
       <c r="F592" t="s">
@@ -31441,7 +31397,7 @@
       <c r="D593" t="s">
         <v>1829</v>
       </c>
-      <c r="E593" t="s">
+      <c r="E593" s="1" t="s">
         <v>1830</v>
       </c>
       <c r="F593" t="s">
@@ -31482,7 +31438,7 @@
       <c r="D594" t="s">
         <v>1833</v>
       </c>
-      <c r="E594" t="s">
+      <c r="E594" s="1" t="s">
         <v>1834</v>
       </c>
       <c r="F594" t="s">
@@ -31523,7 +31479,7 @@
       <c r="D595" t="s">
         <v>1837</v>
       </c>
-      <c r="E595" t="s">
+      <c r="E595" s="1" t="s">
         <v>1838</v>
       </c>
       <c r="F595" t="s">
@@ -31564,7 +31520,7 @@
       <c r="D596" t="s">
         <v>1840</v>
       </c>
-      <c r="E596" t="s">
+      <c r="E596" s="1" t="s">
         <v>1841</v>
       </c>
       <c r="F596" t="s">
@@ -31605,7 +31561,7 @@
       <c r="D597" t="s">
         <v>1540</v>
       </c>
-      <c r="E597" t="s">
+      <c r="E597" s="1" t="s">
         <v>1843</v>
       </c>
       <c r="F597" t="s">
@@ -31646,7 +31602,7 @@
       <c r="D598" t="s">
         <v>1844</v>
       </c>
-      <c r="E598" t="s">
+      <c r="E598" s="1" t="s">
         <v>1845</v>
       </c>
       <c r="F598" t="s">
@@ -31687,7 +31643,7 @@
       <c r="D599" t="s">
         <v>1846</v>
       </c>
-      <c r="E599" t="s">
+      <c r="E599" s="1" t="s">
         <v>1847</v>
       </c>
       <c r="F599" t="s">
@@ -31728,7 +31684,7 @@
       <c r="D600" t="s">
         <v>1581</v>
       </c>
-      <c r="E600" t="s">
+      <c r="E600" s="1" t="s">
         <v>1776</v>
       </c>
       <c r="F600" t="s">
@@ -31769,7 +31725,7 @@
       <c r="D601" t="s">
         <v>1849</v>
       </c>
-      <c r="E601" t="s">
+      <c r="E601" s="1" t="s">
         <v>1850</v>
       </c>
       <c r="F601" t="s">
@@ -31810,7 +31766,7 @@
       <c r="D602" t="s">
         <v>1851</v>
       </c>
-      <c r="E602" t="s">
+      <c r="E602" s="1" t="s">
         <v>1852</v>
       </c>
       <c r="F602" t="s">
@@ -31851,7 +31807,7 @@
       <c r="D603" t="s">
         <v>1855</v>
       </c>
-      <c r="E603" t="s">
+      <c r="E603" s="1" t="s">
         <v>1856</v>
       </c>
       <c r="F603" t="s">
@@ -31892,7 +31848,7 @@
       <c r="D604" t="s">
         <v>1858</v>
       </c>
-      <c r="E604" t="s">
+      <c r="E604" s="1" t="s">
         <v>1859</v>
       </c>
       <c r="F604" t="s">
@@ -31933,7 +31889,7 @@
       <c r="D605" t="s">
         <v>1861</v>
       </c>
-      <c r="E605" t="s">
+      <c r="E605" s="1" t="s">
         <v>1862</v>
       </c>
       <c r="F605" t="s">
@@ -31974,7 +31930,7 @@
       <c r="D606" t="s">
         <v>1608</v>
       </c>
-      <c r="E606" t="s">
+      <c r="E606" s="1" t="s">
         <v>1865</v>
       </c>
       <c r="F606" t="s">
@@ -32015,7 +31971,7 @@
       <c r="D607" t="s">
         <v>1867</v>
       </c>
-      <c r="E607" t="s">
+      <c r="E607" s="1" t="s">
         <v>1868</v>
       </c>
       <c r="F607" t="s">
@@ -32056,7 +32012,7 @@
       <c r="D608" t="s">
         <v>1870</v>
       </c>
-      <c r="E608" t="s">
+      <c r="E608" s="1" t="s">
         <v>1871</v>
       </c>
       <c r="F608" t="s">
@@ -32097,7 +32053,7 @@
       <c r="D609" t="s">
         <v>1872</v>
       </c>
-      <c r="E609" t="s">
+      <c r="E609" s="1" t="s">
         <v>1873</v>
       </c>
       <c r="F609" t="s">
@@ -32138,7 +32094,7 @@
       <c r="D610" t="s">
         <v>1875</v>
       </c>
-      <c r="E610" t="s">
+      <c r="E610" s="1" t="s">
         <v>1876</v>
       </c>
       <c r="F610" t="s">
@@ -32179,7 +32135,7 @@
       <c r="D611" t="s">
         <v>1878</v>
       </c>
-      <c r="E611" t="s">
+      <c r="E611" s="1" t="s">
         <v>1879</v>
       </c>
       <c r="F611" t="s">
@@ -32220,7 +32176,7 @@
       <c r="D612" t="s">
         <v>1880</v>
       </c>
-      <c r="E612" t="s">
+      <c r="E612" s="1" t="s">
         <v>1881</v>
       </c>
       <c r="F612" t="s">
@@ -32261,7 +32217,7 @@
       <c r="D613" t="s">
         <v>1540</v>
       </c>
-      <c r="E613" t="s">
+      <c r="E613" s="1" t="s">
         <v>1882</v>
       </c>
       <c r="F613" t="s">
@@ -32302,7 +32258,7 @@
       <c r="D614" t="s">
         <v>1884</v>
       </c>
-      <c r="E614" t="s">
+      <c r="E614" s="1" t="s">
         <v>1885</v>
       </c>
       <c r="F614" t="s">
@@ -32343,7 +32299,7 @@
       <c r="D615" t="s">
         <v>1887</v>
       </c>
-      <c r="E615" t="s">
+      <c r="E615" s="1" t="s">
         <v>1888</v>
       </c>
       <c r="F615" t="s">
@@ -32384,7 +32340,7 @@
       <c r="D616" t="s">
         <v>1889</v>
       </c>
-      <c r="E616" t="s">
+      <c r="E616" s="1" t="s">
         <v>1890</v>
       </c>
       <c r="F616" t="s">
@@ -32425,7 +32381,7 @@
       <c r="D617" t="s">
         <v>1892</v>
       </c>
-      <c r="E617" t="s">
+      <c r="E617" s="1" t="s">
         <v>1893</v>
       </c>
       <c r="F617" t="s">
@@ -32466,7 +32422,7 @@
       <c r="D618" t="s">
         <v>1895</v>
       </c>
-      <c r="E618" t="s">
+      <c r="E618" s="1" t="s">
         <v>1896</v>
       </c>
       <c r="F618" t="s">
@@ -32507,7 +32463,7 @@
       <c r="D619" t="s">
         <v>1899</v>
       </c>
-      <c r="E619" t="s">
+      <c r="E619" s="1" t="s">
         <v>1900</v>
       </c>
       <c r="F619" t="s">
@@ -32548,7 +32504,7 @@
       <c r="D620" t="s">
         <v>1540</v>
       </c>
-      <c r="E620" t="s">
+      <c r="E620" s="1" t="s">
         <v>1901</v>
       </c>
       <c r="F620" t="s">
@@ -32589,7 +32545,7 @@
       <c r="D621" t="s">
         <v>1581</v>
       </c>
-      <c r="E621" t="s">
+      <c r="E621" s="1" t="s">
         <v>1902</v>
       </c>
       <c r="F621" t="s">
@@ -32630,7 +32586,7 @@
       <c r="D622" t="s">
         <v>1903</v>
       </c>
-      <c r="E622" t="s">
+      <c r="E622" s="1" t="s">
         <v>1904</v>
       </c>
       <c r="F622" t="s">
@@ -32671,7 +32627,7 @@
       <c r="D623" t="s">
         <v>1905</v>
       </c>
-      <c r="E623" t="s">
+      <c r="E623" s="1" t="s">
         <v>1906</v>
       </c>
       <c r="F623" t="s">
@@ -32712,7 +32668,7 @@
       <c r="D624" t="s">
         <v>1907</v>
       </c>
-      <c r="E624" t="s">
+      <c r="E624" s="1" t="s">
         <v>1908</v>
       </c>
       <c r="F624" t="s">
@@ -32753,7 +32709,7 @@
       <c r="D625" t="s">
         <v>1468</v>
       </c>
-      <c r="E625" t="s">
+      <c r="E625" s="1" t="s">
         <v>1910</v>
       </c>
       <c r="F625" t="s">
@@ -32794,7 +32750,7 @@
       <c r="D626" t="s">
         <v>1911</v>
       </c>
-      <c r="E626" t="s">
+      <c r="E626" s="1" t="s">
         <v>1912</v>
       </c>
       <c r="F626" t="s">
@@ -32835,7 +32791,7 @@
       <c r="D627" t="s">
         <v>1915</v>
       </c>
-      <c r="E627" t="s">
+      <c r="E627" s="1" t="s">
         <v>1916</v>
       </c>
       <c r="F627" t="s">
@@ -32876,7 +32832,7 @@
       <c r="D628" t="s">
         <v>1919</v>
       </c>
-      <c r="E628" t="s">
+      <c r="E628" s="1" t="s">
         <v>1920</v>
       </c>
       <c r="F628" t="s">
@@ -32917,7 +32873,7 @@
       <c r="D629" t="s">
         <v>1922</v>
       </c>
-      <c r="E629" t="s">
+      <c r="E629" s="1" t="s">
         <v>1923</v>
       </c>
       <c r="F629" t="s">
@@ -32958,7 +32914,7 @@
       <c r="D630" t="s">
         <v>1925</v>
       </c>
-      <c r="E630" t="s">
+      <c r="E630" s="1" t="s">
         <v>1926</v>
       </c>
       <c r="F630" t="s">
@@ -32999,7 +32955,7 @@
       <c r="D631" t="s">
         <v>1929</v>
       </c>
-      <c r="E631" t="s">
+      <c r="E631" s="1" t="s">
         <v>1930</v>
       </c>
       <c r="F631" t="s">
@@ -33040,7 +32996,7 @@
       <c r="D632" t="s">
         <v>1931</v>
       </c>
-      <c r="E632" t="s">
+      <c r="E632" s="1" t="s">
         <v>1932</v>
       </c>
       <c r="F632" t="s">
@@ -33081,7 +33037,7 @@
       <c r="D633" t="s">
         <v>1934</v>
       </c>
-      <c r="E633" t="s">
+      <c r="E633" s="1" t="s">
         <v>1935</v>
       </c>
       <c r="F633" t="s">
@@ -33122,7 +33078,7 @@
       <c r="D634" t="s">
         <v>1861</v>
       </c>
-      <c r="E634" t="s">
+      <c r="E634" s="1" t="s">
         <v>1936</v>
       </c>
       <c r="F634" t="s">
@@ -33163,7 +33119,7 @@
       <c r="D635" t="s">
         <v>1939</v>
       </c>
-      <c r="E635" t="s">
+      <c r="E635" s="1" t="s">
         <v>1940</v>
       </c>
       <c r="F635" t="s">
@@ -33204,7 +33160,7 @@
       <c r="D636" t="s">
         <v>1942</v>
       </c>
-      <c r="E636" t="s">
+      <c r="E636" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F636" t="s">
@@ -33245,7 +33201,7 @@
       <c r="D637" t="s">
         <v>1944</v>
       </c>
-      <c r="E637" t="s">
+      <c r="E637" s="1" t="s">
         <v>1945</v>
       </c>
       <c r="F637" t="s">
@@ -33286,7 +33242,7 @@
       <c r="D638" t="s">
         <v>1947</v>
       </c>
-      <c r="E638" t="s">
+      <c r="E638" s="1" t="s">
         <v>1948</v>
       </c>
       <c r="F638" t="s">
@@ -33327,7 +33283,7 @@
       <c r="D639" t="s">
         <v>1892</v>
       </c>
-      <c r="E639" t="s">
+      <c r="E639" s="1" t="s">
         <v>1949</v>
       </c>
       <c r="F639" t="s">
@@ -33368,7 +33324,7 @@
       <c r="D640" t="s">
         <v>1951</v>
       </c>
-      <c r="E640" t="s">
+      <c r="E640" s="1" t="s">
         <v>1900</v>
       </c>
       <c r="F640" t="s">
@@ -33409,7 +33365,7 @@
       <c r="D641" t="s">
         <v>1540</v>
       </c>
-      <c r="E641" t="s">
+      <c r="E641" s="1" t="s">
         <v>1953</v>
       </c>
       <c r="F641" t="s">
@@ -33450,7 +33406,7 @@
       <c r="D642" t="s">
         <v>1540</v>
       </c>
-      <c r="E642" t="s">
+      <c r="E642" s="1" t="s">
         <v>1954</v>
       </c>
       <c r="F642" t="s">
@@ -33491,7 +33447,7 @@
       <c r="D643" t="s">
         <v>1957</v>
       </c>
-      <c r="E643" t="s">
+      <c r="E643" s="1" t="s">
         <v>1904</v>
       </c>
       <c r="F643" t="s">
@@ -33532,7 +33488,7 @@
       <c r="D644" t="s">
         <v>1959</v>
       </c>
-      <c r="E644" t="s">
+      <c r="E644" s="1" t="s">
         <v>1960</v>
       </c>
       <c r="F644" t="s">
@@ -33573,7 +33529,7 @@
       <c r="D645" t="s">
         <v>1540</v>
       </c>
-      <c r="E645" t="s">
+      <c r="E645" s="1" t="s">
         <v>1963</v>
       </c>
       <c r="F645" t="s">
@@ -33614,7 +33570,7 @@
       <c r="D646" t="s">
         <v>1581</v>
       </c>
-      <c r="E646" t="s">
+      <c r="E646" s="1" t="s">
         <v>1964</v>
       </c>
       <c r="F646" t="s">
@@ -33655,7 +33611,7 @@
       <c r="D647" t="s">
         <v>1581</v>
       </c>
-      <c r="E647" t="s">
+      <c r="E647" s="1" t="s">
         <v>1964</v>
       </c>
       <c r="F647" t="s">
@@ -33696,7 +33652,7 @@
       <c r="D648" t="s">
         <v>1581</v>
       </c>
-      <c r="E648" t="s">
+      <c r="E648" s="1" t="s">
         <v>1965</v>
       </c>
       <c r="F648" t="s">
@@ -33737,7 +33693,7 @@
       <c r="D649" t="s">
         <v>1581</v>
       </c>
-      <c r="E649" t="s">
+      <c r="E649" s="1" t="s">
         <v>1966</v>
       </c>
       <c r="F649" t="s">
@@ -33778,7 +33734,7 @@
       <c r="D650" t="s">
         <v>1581</v>
       </c>
-      <c r="E650" t="s">
+      <c r="E650" s="1" t="s">
         <v>1966</v>
       </c>
       <c r="F650" t="s">
@@ -33819,7 +33775,7 @@
       <c r="D651" t="s">
         <v>1968</v>
       </c>
-      <c r="E651" t="s">
+      <c r="E651" s="1" t="s">
         <v>1969</v>
       </c>
       <c r="F651" t="s">
@@ -33860,7 +33816,7 @@
       <c r="D652" t="s">
         <v>1970</v>
       </c>
-      <c r="E652" t="s">
+      <c r="E652" s="1" t="s">
         <v>1971</v>
       </c>
       <c r="F652" t="s">
@@ -33901,7 +33857,7 @@
       <c r="D653" t="s">
         <v>1972</v>
       </c>
-      <c r="E653" t="s">
+      <c r="E653" s="1" t="s">
         <v>1828</v>
       </c>
       <c r="F653" t="s">
@@ -33942,7 +33898,7 @@
       <c r="D654" t="s">
         <v>1975</v>
       </c>
-      <c r="E654" t="s">
+      <c r="E654" s="1" t="s">
         <v>1976</v>
       </c>
       <c r="F654" t="s">
@@ -33983,7 +33939,7 @@
       <c r="D655" t="s">
         <v>1979</v>
       </c>
-      <c r="E655" t="s">
+      <c r="E655" s="1" t="s">
         <v>1926</v>
       </c>
       <c r="F655" t="s">
@@ -34024,7 +33980,7 @@
       <c r="D656" t="s">
         <v>1980</v>
       </c>
-      <c r="E656" t="s">
+      <c r="E656" s="1" t="s">
         <v>1981</v>
       </c>
       <c r="F656" t="s">
@@ -34065,7 +34021,7 @@
       <c r="D657" t="s">
         <v>990</v>
       </c>
-      <c r="E657" t="s">
+      <c r="E657" s="1" t="s">
         <v>1982</v>
       </c>
       <c r="F657" t="s">
@@ -34106,7 +34062,7 @@
       <c r="D658" t="s">
         <v>990</v>
       </c>
-      <c r="E658" t="s">
+      <c r="E658" s="1" t="s">
         <v>1984</v>
       </c>
       <c r="F658" t="s">
@@ -34147,7 +34103,7 @@
       <c r="D659" t="s">
         <v>1468</v>
       </c>
-      <c r="E659" t="s">
+      <c r="E659" s="1" t="s">
         <v>1910</v>
       </c>
       <c r="F659" t="s">
@@ -34188,7 +34144,7 @@
       <c r="D660" t="s">
         <v>1987</v>
       </c>
-      <c r="E660" t="s">
+      <c r="E660" s="1" t="s">
         <v>1988</v>
       </c>
       <c r="F660" t="s">
@@ -34229,7 +34185,7 @@
       <c r="D661" t="s">
         <v>1330</v>
       </c>
-      <c r="E661" t="s">
+      <c r="E661" s="1" t="s">
         <v>1990</v>
       </c>
       <c r="F661" t="s">
@@ -34270,7 +34226,7 @@
       <c r="D662" t="s">
         <v>1581</v>
       </c>
-      <c r="E662" t="s">
+      <c r="E662" s="1" t="s">
         <v>1992</v>
       </c>
       <c r="F662" t="s">
@@ -34311,7 +34267,7 @@
       <c r="D663" t="s">
         <v>1581</v>
       </c>
-      <c r="E663" t="s">
+      <c r="E663" s="1" t="s">
         <v>1992</v>
       </c>
       <c r="F663" t="s">
@@ -34352,7 +34308,7 @@
       <c r="D664" t="s">
         <v>1994</v>
       </c>
-      <c r="E664" t="s">
+      <c r="E664" s="1" t="s">
         <v>1995</v>
       </c>
       <c r="F664" t="s">
@@ -34393,7 +34349,7 @@
       <c r="D665" t="s">
         <v>1997</v>
       </c>
-      <c r="E665" t="s">
+      <c r="E665" s="1" t="s">
         <v>1998</v>
       </c>
       <c r="F665" t="s">
@@ -34434,7 +34390,7 @@
       <c r="D666" t="s">
         <v>2000</v>
       </c>
-      <c r="E666" t="s">
+      <c r="E666" s="1" t="s">
         <v>2001</v>
       </c>
       <c r="F666" t="s">
@@ -34475,7 +34431,7 @@
       <c r="D667" t="s">
         <v>2002</v>
       </c>
-      <c r="E667" t="s">
+      <c r="E667" s="1" t="s">
         <v>2003</v>
       </c>
       <c r="F667" t="s">
@@ -34516,7 +34472,7 @@
       <c r="D668" t="s">
         <v>2004</v>
       </c>
-      <c r="E668" t="s">
+      <c r="E668" s="1" t="s">
         <v>2005</v>
       </c>
       <c r="F668" t="s">
@@ -34557,7 +34513,7 @@
       <c r="D669" t="s">
         <v>2006</v>
       </c>
-      <c r="E669" t="s">
+      <c r="E669" s="1" t="s">
         <v>2007</v>
       </c>
       <c r="F669" t="s">
@@ -34598,7 +34554,7 @@
       <c r="D670" t="s">
         <v>1951</v>
       </c>
-      <c r="E670" t="s">
+      <c r="E670" s="1" t="s">
         <v>1900</v>
       </c>
       <c r="F670" t="s">
@@ -34639,7 +34595,7 @@
       <c r="D671" t="s">
         <v>2010</v>
       </c>
-      <c r="E671" t="s">
+      <c r="E671" s="1" t="s">
         <v>2011</v>
       </c>
       <c r="F671" t="s">
@@ -34680,7 +34636,7 @@
       <c r="D672" t="s">
         <v>1540</v>
       </c>
-      <c r="E672" t="s">
+      <c r="E672" s="1" t="s">
         <v>2013</v>
       </c>
       <c r="F672" t="s">
@@ -34721,7 +34677,7 @@
       <c r="D673" t="s">
         <v>2014</v>
       </c>
-      <c r="E673" t="s">
+      <c r="E673" s="1" t="s">
         <v>2015</v>
       </c>
       <c r="F673" t="s">
@@ -34762,7 +34718,7 @@
       <c r="D674" t="s">
         <v>2017</v>
       </c>
-      <c r="E674" t="s">
+      <c r="E674" s="1" t="s">
         <v>1910</v>
       </c>
       <c r="F674" t="s">
@@ -34803,7 +34759,7 @@
       <c r="D675" t="s">
         <v>1581</v>
       </c>
-      <c r="E675" t="s">
+      <c r="E675" s="1" t="s">
         <v>2019</v>
       </c>
       <c r="F675" t="s">
@@ -34844,7 +34800,7 @@
       <c r="D676" t="s">
         <v>2020</v>
       </c>
-      <c r="E676" t="s">
+      <c r="E676" s="1" t="s">
         <v>2021</v>
       </c>
       <c r="F676" t="s">
@@ -34885,7 +34841,7 @@
       <c r="D677" t="s">
         <v>1540</v>
       </c>
-      <c r="E677" t="s">
+      <c r="E677" s="1" t="s">
         <v>2023</v>
       </c>
       <c r="F677" t="s">
@@ -34926,7 +34882,7 @@
       <c r="D678" t="s">
         <v>2025</v>
       </c>
-      <c r="E678" t="s">
+      <c r="E678" s="1" t="s">
         <v>2026</v>
       </c>
       <c r="F678" t="s">
@@ -34967,7 +34923,7 @@
       <c r="D679" t="s">
         <v>2028</v>
       </c>
-      <c r="E679" t="s">
+      <c r="E679" s="1" t="s">
         <v>2029</v>
       </c>
       <c r="F679" t="s">
@@ -35008,7 +34964,7 @@
       <c r="D680" t="s">
         <v>1540</v>
       </c>
-      <c r="E680" t="s">
+      <c r="E680" s="1" t="s">
         <v>2031</v>
       </c>
       <c r="F680" t="s">
@@ -35049,7 +35005,7 @@
       <c r="D681" t="s">
         <v>2033</v>
       </c>
-      <c r="E681" t="s">
+      <c r="E681" s="1" t="s">
         <v>2034</v>
       </c>
       <c r="F681" t="s">
@@ -35090,7 +35046,7 @@
       <c r="D682" t="s">
         <v>2036</v>
       </c>
-      <c r="E682" t="s">
+      <c r="E682" s="1" t="s">
         <v>2037</v>
       </c>
       <c r="F682" t="s">
@@ -35131,7 +35087,7 @@
       <c r="D683" t="s">
         <v>2040</v>
       </c>
-      <c r="E683" t="s">
+      <c r="E683" s="1" t="s">
         <v>2041</v>
       </c>
       <c r="F683" t="s">
@@ -35172,7 +35128,7 @@
       <c r="D684" t="s">
         <v>1486</v>
       </c>
-      <c r="E684" t="s">
+      <c r="E684" s="1" t="s">
         <v>2043</v>
       </c>
       <c r="F684" t="s">
@@ -35213,7 +35169,7 @@
       <c r="D685" t="s">
         <v>1581</v>
       </c>
-      <c r="E685" t="s">
+      <c r="E685" s="1" t="s">
         <v>2044</v>
       </c>
       <c r="F685" t="s">
@@ -35254,7 +35210,7 @@
       <c r="D686" t="s">
         <v>2046</v>
       </c>
-      <c r="E686" t="s">
+      <c r="E686" s="1" t="s">
         <v>2047</v>
       </c>
       <c r="F686" t="s">
@@ -35295,7 +35251,7 @@
       <c r="D687" t="s">
         <v>2049</v>
       </c>
-      <c r="E687" t="s">
+      <c r="E687" s="1" t="s">
         <v>2050</v>
       </c>
       <c r="F687" t="s">
@@ -35336,7 +35292,7 @@
       <c r="D688" t="s">
         <v>2054</v>
       </c>
-      <c r="E688" t="s">
+      <c r="E688" s="1" t="s">
         <v>733</v>
       </c>
       <c r="F688" t="s">
@@ -35377,7 +35333,7 @@
       <c r="D689" t="s">
         <v>1206</v>
       </c>
-      <c r="E689" t="s">
+      <c r="E689" s="1" t="s">
         <v>2055</v>
       </c>
       <c r="F689" t="s">
@@ -35418,7 +35374,7 @@
       <c r="D690" t="s">
         <v>1486</v>
       </c>
-      <c r="E690" t="s">
+      <c r="E690" s="1" t="s">
         <v>2057</v>
       </c>
       <c r="F690" t="s">
@@ -35459,7 +35415,7 @@
       <c r="D691" t="s">
         <v>2058</v>
       </c>
-      <c r="E691" t="s">
+      <c r="E691" s="1" t="s">
         <v>1948</v>
       </c>
       <c r="F691" t="s">
@@ -35500,7 +35456,7 @@
       <c r="D692" t="s">
         <v>1540</v>
       </c>
-      <c r="E692" t="s">
+      <c r="E692" s="1" t="s">
         <v>2060</v>
       </c>
       <c r="F692" t="s">
@@ -35541,7 +35497,7 @@
       <c r="D693" t="s">
         <v>2061</v>
       </c>
-      <c r="E693" t="s">
+      <c r="E693" s="1" t="s">
         <v>2062</v>
       </c>
       <c r="F693" t="s">
@@ -35582,7 +35538,7 @@
       <c r="D694" t="s">
         <v>2064</v>
       </c>
-      <c r="E694" t="s">
+      <c r="E694" s="1" t="s">
         <v>2065</v>
       </c>
       <c r="F694" t="s">
@@ -35623,7 +35579,7 @@
       <c r="D695" t="s">
         <v>2067</v>
       </c>
-      <c r="E695" t="s">
+      <c r="E695" s="1" t="s">
         <v>2068</v>
       </c>
       <c r="F695" t="s">
@@ -35664,7 +35620,7 @@
       <c r="D696" t="s">
         <v>2069</v>
       </c>
-      <c r="E696" t="s">
+      <c r="E696" s="1" t="s">
         <v>2070</v>
       </c>
       <c r="F696" t="s">
@@ -35705,7 +35661,7 @@
       <c r="D697" t="s">
         <v>2071</v>
       </c>
-      <c r="E697" t="s">
+      <c r="E697" s="1" t="s">
         <v>2072</v>
       </c>
       <c r="F697" t="s">
@@ -35746,7 +35702,7 @@
       <c r="D698" t="s">
         <v>2035</v>
       </c>
-      <c r="E698" t="s">
+      <c r="E698" s="1" t="s">
         <v>2037</v>
       </c>
       <c r="F698" t="s">
@@ -35787,7 +35743,7 @@
       <c r="D699" t="s">
         <v>2075</v>
       </c>
-      <c r="E699" t="s">
+      <c r="E699" s="1" t="s">
         <v>2076</v>
       </c>
       <c r="F699" t="s">
@@ -35828,7 +35784,7 @@
       <c r="D700" t="s">
         <v>1486</v>
       </c>
-      <c r="E700" t="s">
+      <c r="E700" s="1" t="s">
         <v>2077</v>
       </c>
       <c r="F700" t="s">
@@ -35869,7 +35825,7 @@
       <c r="D701" t="s">
         <v>1332</v>
       </c>
-      <c r="E701" t="s">
+      <c r="E701" s="1" t="s">
         <v>2078</v>
       </c>
       <c r="F701" t="s">
@@ -35910,7 +35866,7 @@
       <c r="D702" t="s">
         <v>2080</v>
       </c>
-      <c r="E702" t="s">
+      <c r="E702" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F702" t="s">
@@ -35951,7 +35907,7 @@
       <c r="D703" t="s">
         <v>2082</v>
       </c>
-      <c r="E703" t="s">
+      <c r="E703" s="1" t="s">
         <v>372</v>
       </c>
       <c r="F703" t="s">
@@ -35992,7 +35948,7 @@
       <c r="D704" t="s">
         <v>2083</v>
       </c>
-      <c r="E704" t="s">
+      <c r="E704" s="1" t="s">
         <v>2084</v>
       </c>
       <c r="F704" t="s">
@@ -36033,7 +35989,7 @@
       <c r="D705" t="s">
         <v>2085</v>
       </c>
-      <c r="E705" t="s">
+      <c r="E705" s="1" t="s">
         <v>2086</v>
       </c>
       <c r="F705" t="s">
@@ -36074,7 +36030,7 @@
       <c r="D706" t="s">
         <v>1540</v>
       </c>
-      <c r="E706" t="s">
+      <c r="E706" s="1" t="s">
         <v>2087</v>
       </c>
       <c r="F706" t="s">
@@ -36115,7 +36071,7 @@
       <c r="D707" t="s">
         <v>1486</v>
       </c>
-      <c r="E707" t="s">
+      <c r="E707" s="1" t="s">
         <v>2089</v>
       </c>
       <c r="F707" t="s">
@@ -36156,7 +36112,7 @@
       <c r="D708" t="s">
         <v>1332</v>
       </c>
-      <c r="E708" t="s">
+      <c r="E708" s="1" t="s">
         <v>2091</v>
       </c>
       <c r="F708" t="s">
@@ -36197,7 +36153,7 @@
       <c r="D709" t="s">
         <v>2092</v>
       </c>
-      <c r="E709" t="s">
+      <c r="E709" s="1" t="s">
         <v>2093</v>
       </c>
       <c r="F709" t="s">
@@ -36238,7 +36194,7 @@
       <c r="D710" t="s">
         <v>2094</v>
       </c>
-      <c r="E710" t="s">
+      <c r="E710" s="1" t="s">
         <v>2095</v>
       </c>
       <c r="F710" t="s">
@@ -36279,7 +36235,7 @@
       <c r="D711" t="s">
         <v>1624</v>
       </c>
-      <c r="E711" t="s">
+      <c r="E711" s="1" t="s">
         <v>2096</v>
       </c>
       <c r="F711" t="s">
@@ -36320,7 +36276,7 @@
       <c r="D712" t="s">
         <v>1624</v>
       </c>
-      <c r="E712" t="s">
+      <c r="E712" s="1" t="s">
         <v>2097</v>
       </c>
       <c r="F712" t="s">
@@ -36361,7 +36317,7 @@
       <c r="D713" t="s">
         <v>2099</v>
       </c>
-      <c r="E713" t="s">
+      <c r="E713" s="1" t="s">
         <v>2100</v>
       </c>
       <c r="F713" t="s">
@@ -36402,7 +36358,7 @@
       <c r="D714" t="s">
         <v>2102</v>
       </c>
-      <c r="E714" t="s">
+      <c r="E714" s="1" t="s">
         <v>2103</v>
       </c>
       <c r="F714" t="s">
@@ -36443,7 +36399,7 @@
       <c r="D715" t="s">
         <v>2104</v>
       </c>
-      <c r="E715" t="s">
+      <c r="E715" s="1" t="s">
         <v>403</v>
       </c>
       <c r="F715" t="s">
@@ -36484,7 +36440,7 @@
       <c r="D716" t="s">
         <v>1486</v>
       </c>
-      <c r="E716" t="s">
+      <c r="E716" s="1" t="s">
         <v>2105</v>
       </c>
       <c r="F716" t="s">
@@ -36525,7 +36481,7 @@
       <c r="D717" t="s">
         <v>2106</v>
       </c>
-      <c r="E717" t="s">
+      <c r="E717" s="1" t="s">
         <v>2072</v>
       </c>
       <c r="F717" t="s">
@@ -36566,7 +36522,7 @@
       <c r="D718" t="s">
         <v>2109</v>
       </c>
-      <c r="E718" t="s">
+      <c r="E718" s="1" t="s">
         <v>2110</v>
       </c>
       <c r="F718" t="s">
@@ -36607,7 +36563,7 @@
       <c r="D719" t="s">
         <v>1540</v>
       </c>
-      <c r="E719" t="s">
+      <c r="E719" s="1" t="s">
         <v>2112</v>
       </c>
       <c r="F719" t="s">
@@ -36648,7 +36604,7 @@
       <c r="D720" t="s">
         <v>2113</v>
       </c>
-      <c r="E720" t="s">
+      <c r="E720" s="1" t="s">
         <v>2114</v>
       </c>
       <c r="F720" t="s">
@@ -36689,7 +36645,7 @@
       <c r="D721" t="s">
         <v>2115</v>
       </c>
-      <c r="E721" t="s">
+      <c r="E721" s="1" t="s">
         <v>2116</v>
       </c>
       <c r="F721" t="s">
@@ -36730,7 +36686,7 @@
       <c r="D722" t="s">
         <v>2118</v>
       </c>
-      <c r="E722" t="s">
+      <c r="E722" s="1" t="s">
         <v>2119</v>
       </c>
       <c r="F722" t="s">
@@ -36771,7 +36727,7 @@
       <c r="D723" t="s">
         <v>1486</v>
       </c>
-      <c r="E723" t="s">
+      <c r="E723" s="1" t="s">
         <v>2105</v>
       </c>
       <c r="F723" t="s">
@@ -36812,7 +36768,7 @@
       <c r="D724" t="s">
         <v>1624</v>
       </c>
-      <c r="E724" t="s">
+      <c r="E724" s="1" t="s">
         <v>2120</v>
       </c>
       <c r="F724" t="s">
@@ -36853,7 +36809,7 @@
       <c r="D725" t="s">
         <v>2113</v>
       </c>
-      <c r="E725" t="s">
+      <c r="E725" s="1" t="s">
         <v>2121</v>
       </c>
       <c r="F725" t="s">
@@ -36894,7 +36850,7 @@
       <c r="D726" t="s">
         <v>1624</v>
       </c>
-      <c r="E726" t="s">
+      <c r="E726" s="1" t="s">
         <v>2122</v>
       </c>
       <c r="F726" t="s">
@@ -36935,7 +36891,7 @@
       <c r="D727" t="s">
         <v>2113</v>
       </c>
-      <c r="E727" t="s">
+      <c r="E727" s="1" t="s">
         <v>2123</v>
       </c>
       <c r="F727" t="s">
@@ -36976,7 +36932,7 @@
       <c r="D728" t="s">
         <v>2125</v>
       </c>
-      <c r="E728" t="s">
+      <c r="E728" s="1" t="s">
         <v>1298</v>
       </c>
       <c r="F728" t="s">
@@ -37017,7 +36973,7 @@
       <c r="D729" t="s">
         <v>2127</v>
       </c>
-      <c r="E729" t="s">
+      <c r="E729" s="1" t="s">
         <v>2128</v>
       </c>
       <c r="F729" t="s">
@@ -37058,7 +37014,7 @@
       <c r="D730" t="s">
         <v>1486</v>
       </c>
-      <c r="E730" t="s">
+      <c r="E730" s="1" t="s">
         <v>2130</v>
       </c>
       <c r="F730" t="s">
@@ -37099,7 +37055,7 @@
       <c r="D731" t="s">
         <v>2132</v>
       </c>
-      <c r="E731" t="s">
+      <c r="E731" s="1" t="s">
         <v>2133</v>
       </c>
       <c r="F731" t="s">
@@ -37140,7 +37096,7 @@
       <c r="D732" t="s">
         <v>1540</v>
       </c>
-      <c r="E732" t="s">
+      <c r="E732" s="1" t="s">
         <v>2135</v>
       </c>
       <c r="F732" t="s">
@@ -37181,7 +37137,7 @@
       <c r="D733" t="s">
         <v>1540</v>
       </c>
-      <c r="E733" t="s">
+      <c r="E733" s="1" t="s">
         <v>2136</v>
       </c>
       <c r="F733" t="s">
@@ -37222,7 +37178,7 @@
       <c r="D734" t="s">
         <v>2137</v>
       </c>
-      <c r="E734" t="s">
+      <c r="E734" s="1" t="s">
         <v>2138</v>
       </c>
       <c r="F734" t="s">
@@ -37263,7 +37219,7 @@
       <c r="D735" t="s">
         <v>2113</v>
       </c>
-      <c r="E735" t="s">
+      <c r="E735" s="1" t="s">
         <v>2140</v>
       </c>
       <c r="F735" t="s">
@@ -37304,7 +37260,7 @@
       <c r="D736" t="s">
         <v>2113</v>
       </c>
-      <c r="E736" t="s">
+      <c r="E736" s="1" t="s">
         <v>2141</v>
       </c>
       <c r="F736" t="s">
@@ -37345,7 +37301,7 @@
       <c r="D737" t="s">
         <v>2113</v>
       </c>
-      <c r="E737" t="s">
+      <c r="E737" s="1" t="s">
         <v>2142</v>
       </c>
       <c r="F737" t="s">
@@ -37386,7 +37342,7 @@
       <c r="D738" t="s">
         <v>2113</v>
       </c>
-      <c r="E738" t="s">
+      <c r="E738" s="1" t="s">
         <v>2143</v>
       </c>
       <c r="F738" t="s">
@@ -37427,7 +37383,7 @@
       <c r="D739" t="s">
         <v>2144</v>
       </c>
-      <c r="E739" t="s">
+      <c r="E739" s="1" t="s">
         <v>2145</v>
       </c>
       <c r="F739" t="s">
@@ -37468,7 +37424,7 @@
       <c r="D740" t="s">
         <v>2144</v>
       </c>
-      <c r="E740" t="s">
+      <c r="E740" s="1" t="s">
         <v>2146</v>
       </c>
       <c r="F740" t="s">
@@ -37509,7 +37465,7 @@
       <c r="D741" t="s">
         <v>2148</v>
       </c>
-      <c r="E741" t="s">
+      <c r="E741" s="1" t="s">
         <v>2149</v>
       </c>
       <c r="F741" t="s">
@@ -37550,7 +37506,7 @@
       <c r="D742" t="s">
         <v>1486</v>
       </c>
-      <c r="E742" t="s">
+      <c r="E742" s="1" t="s">
         <v>2150</v>
       </c>
       <c r="F742" t="s">
@@ -37591,7 +37547,7 @@
       <c r="D743" t="s">
         <v>2152</v>
       </c>
-      <c r="E743" t="s">
+      <c r="E743" s="1" t="s">
         <v>2153</v>
       </c>
       <c r="F743" t="s">
@@ -37632,7 +37588,7 @@
       <c r="D744" t="s">
         <v>1907</v>
       </c>
-      <c r="E744" t="s">
+      <c r="E744" s="1" t="s">
         <v>2110</v>
       </c>
       <c r="F744" t="s">
@@ -37673,7 +37629,7 @@
       <c r="D745" t="s">
         <v>2156</v>
       </c>
-      <c r="E745" t="s">
+      <c r="E745" s="1" t="s">
         <v>2157</v>
       </c>
       <c r="F745" t="s">
@@ -37714,7 +37670,7 @@
       <c r="D746" t="s">
         <v>2033</v>
       </c>
-      <c r="E746" t="s">
+      <c r="E746" s="1" t="s">
         <v>2158</v>
       </c>
       <c r="F746" t="s">
@@ -37755,7 +37711,7 @@
       <c r="D747" t="s">
         <v>1540</v>
       </c>
-      <c r="E747" t="s">
+      <c r="E747" s="1" t="s">
         <v>2160</v>
       </c>
       <c r="F747" t="s">
@@ -37796,7 +37752,7 @@
       <c r="D748" t="s">
         <v>2161</v>
       </c>
-      <c r="E748" t="s">
+      <c r="E748" s="1" t="s">
         <v>2162</v>
       </c>
       <c r="F748" t="s">
@@ -37837,7 +37793,7 @@
       <c r="D749" t="s">
         <v>2165</v>
       </c>
-      <c r="E749" t="s">
+      <c r="E749" s="1" t="s">
         <v>2166</v>
       </c>
       <c r="F749" t="s">
@@ -37878,7 +37834,7 @@
       <c r="D750" t="s">
         <v>2165</v>
       </c>
-      <c r="E750" t="s">
+      <c r="E750" s="1" t="s">
         <v>2169</v>
       </c>
       <c r="F750" t="s">
@@ -37919,7 +37875,7 @@
       <c r="D751" t="s">
         <v>2170</v>
       </c>
-      <c r="E751" t="s">
+      <c r="E751" s="1" t="s">
         <v>2171</v>
       </c>
       <c r="F751" t="s">
@@ -37960,7 +37916,7 @@
       <c r="D752" t="s">
         <v>2170</v>
       </c>
-      <c r="E752" t="s">
+      <c r="E752" s="1" t="s">
         <v>2172</v>
       </c>
       <c r="F752" t="s">
@@ -38001,7 +37957,7 @@
       <c r="D753" t="s">
         <v>2173</v>
       </c>
-      <c r="E753" t="s">
+      <c r="E753" s="1" t="s">
         <v>511</v>
       </c>
       <c r="F753" t="s">
@@ -38042,7 +37998,7 @@
       <c r="D754" t="s">
         <v>1540</v>
       </c>
-      <c r="E754" t="s">
+      <c r="E754" s="1" t="s">
         <v>2174</v>
       </c>
       <c r="F754" t="s">
@@ -38083,7 +38039,7 @@
       <c r="D755" t="s">
         <v>1540</v>
       </c>
-      <c r="E755" t="s">
+      <c r="E755" s="1" t="s">
         <v>2175</v>
       </c>
       <c r="F755" t="s">
@@ -38124,7 +38080,7 @@
       <c r="D756" t="s">
         <v>2165</v>
       </c>
-      <c r="E756" t="s">
+      <c r="E756" s="1" t="s">
         <v>2177</v>
       </c>
       <c r="F756" t="s">
@@ -38165,7 +38121,7 @@
       <c r="D757" t="s">
         <v>2165</v>
       </c>
-      <c r="E757" t="s">
+      <c r="E757" s="1" t="s">
         <v>2179</v>
       </c>
       <c r="F757" t="s">
@@ -38206,7 +38162,7 @@
       <c r="D758" t="s">
         <v>2180</v>
       </c>
-      <c r="E758" t="s">
+      <c r="E758" s="1" t="s">
         <v>2181</v>
       </c>
       <c r="F758" t="s">
@@ -38247,7 +38203,7 @@
       <c r="D759" t="s">
         <v>1540</v>
       </c>
-      <c r="E759" t="s">
+      <c r="E759" s="1" t="s">
         <v>2183</v>
       </c>
       <c r="F759" t="s">
@@ -38288,7 +38244,7 @@
       <c r="D760" t="s">
         <v>2165</v>
       </c>
-      <c r="E760" t="s">
+      <c r="E760" s="1" t="s">
         <v>2185</v>
       </c>
       <c r="F760" t="s">
@@ -38329,7 +38285,7 @@
       <c r="D761" t="s">
         <v>2165</v>
       </c>
-      <c r="E761" t="s">
+      <c r="E761" s="1" t="s">
         <v>2187</v>
       </c>
       <c r="F761" t="s">
@@ -38370,7 +38326,7 @@
       <c r="D762" t="s">
         <v>2189</v>
       </c>
-      <c r="E762" t="s">
+      <c r="E762" s="1" t="s">
         <v>2190</v>
       </c>
       <c r="F762" t="s">
@@ -38411,7 +38367,7 @@
       <c r="D763" t="s">
         <v>2191</v>
       </c>
-      <c r="E763" t="s">
+      <c r="E763" s="1" t="s">
         <v>2192</v>
       </c>
       <c r="F763" t="s">
@@ -38452,7 +38408,7 @@
       <c r="D764" t="s">
         <v>2194</v>
       </c>
-      <c r="E764" t="s">
+      <c r="E764" s="1" t="s">
         <v>2195</v>
       </c>
       <c r="F764" t="s">
@@ -38493,7 +38449,7 @@
       <c r="D765" t="s">
         <v>2196</v>
       </c>
-      <c r="E765" t="s">
+      <c r="E765" s="2" t="s">
         <v>2197</v>
       </c>
       <c r="F765" t="s">
@@ -38534,7 +38490,7 @@
       <c r="D766" t="s">
         <v>2199</v>
       </c>
-      <c r="E766" t="s">
+      <c r="E766" s="2" t="s">
         <v>2200</v>
       </c>
       <c r="F766" t="s">
@@ -38575,7 +38531,7 @@
       <c r="D767" t="s">
         <v>2180</v>
       </c>
-      <c r="E767" t="s">
+      <c r="E767" s="2" t="s">
         <v>2181</v>
       </c>
       <c r="F767" t="s">
@@ -38616,7 +38572,7 @@
       <c r="D768" t="s">
         <v>2201</v>
       </c>
-      <c r="E768" t="s">
+      <c r="E768" s="2" t="s">
         <v>2181</v>
       </c>
       <c r="F768" t="s">
@@ -38657,7 +38613,7 @@
       <c r="D769" t="s">
         <v>2202</v>
       </c>
-      <c r="E769" t="s">
+      <c r="E769" s="2" t="s">
         <v>2203</v>
       </c>
       <c r="F769" t="s">
@@ -38698,7 +38654,7 @@
       <c r="D770" t="s">
         <v>2204</v>
       </c>
-      <c r="E770" t="s">
+      <c r="E770" s="2" t="s">
         <v>2205</v>
       </c>
       <c r="F770" t="s">
@@ -38739,7 +38695,7 @@
       <c r="D771" t="s">
         <v>2207</v>
       </c>
-      <c r="E771" t="s">
+      <c r="E771" s="2" t="s">
         <v>2208</v>
       </c>
       <c r="F771" t="s">
@@ -38780,7 +38736,7 @@
       <c r="D772" t="s">
         <v>2209</v>
       </c>
-      <c r="E772" t="s">
+      <c r="E772" s="2" t="s">
         <v>372</v>
       </c>
       <c r="F772" t="s">
@@ -38821,7 +38777,7 @@
       <c r="D773" t="s">
         <v>2165</v>
       </c>
-      <c r="E773" t="s">
+      <c r="E773" s="2" t="s">
         <v>2210</v>
       </c>
       <c r="F773" t="s">
@@ -38862,7 +38818,7 @@
       <c r="D774" t="s">
         <v>2211</v>
       </c>
-      <c r="E774" t="s">
+      <c r="E774" s="2" t="s">
         <v>2212</v>
       </c>
       <c r="F774" t="s">
@@ -38903,7 +38859,7 @@
       <c r="D775" t="s">
         <v>2180</v>
       </c>
-      <c r="E775" t="s">
+      <c r="E775" s="2" t="s">
         <v>2181</v>
       </c>
       <c r="F775" t="s">
@@ -38944,7 +38900,7 @@
       <c r="D776" t="s">
         <v>1540</v>
       </c>
-      <c r="E776" t="s">
+      <c r="E776" s="2" t="s">
         <v>2213</v>
       </c>
       <c r="F776" t="s">
@@ -38985,7 +38941,7 @@
       <c r="D777" t="s">
         <v>1540</v>
       </c>
-      <c r="E777" t="s">
+      <c r="E777" s="2" t="s">
         <v>2214</v>
       </c>
       <c r="F777" t="s">
@@ -39026,7 +38982,7 @@
       <c r="D778" t="s">
         <v>2215</v>
       </c>
-      <c r="E778" t="s">
+      <c r="E778" s="2" t="s">
         <v>2216</v>
       </c>
       <c r="F778" t="s">
@@ -39067,8 +39023,8 @@
       <c r="D779" t="s">
         <v>2218</v>
       </c>
-      <c r="E779" t="s">
-        <v>2219</v>
+      <c r="E779" s="2">
+        <v>82455</v>
       </c>
       <c r="F779" t="s">
         <v>196</v>
@@ -39103,13 +39059,13 @@
         <v>54</v>
       </c>
       <c r="C780" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D780" t="s">
         <v>2220</v>
       </c>
-      <c r="D780" t="s">
-        <v>2221</v>
-      </c>
-      <c r="E780" t="s">
-        <v>2222</v>
+      <c r="E780" s="2">
+        <v>430000</v>
       </c>
       <c r="F780" t="s">
         <v>196</v>
@@ -39149,8 +39105,8 @@
       <c r="D781" t="s">
         <v>1540</v>
       </c>
-      <c r="E781" t="s">
-        <v>2223</v>
+      <c r="E781" s="2">
+        <v>109538</v>
       </c>
       <c r="F781" t="s">
         <v>196</v>
@@ -39185,13 +39141,13 @@
         <v>54</v>
       </c>
       <c r="C782" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="D782" t="s">
-        <v>2224</v>
-      </c>
-      <c r="E782" t="s">
-        <v>2225</v>
+        <v>2221</v>
+      </c>
+      <c r="E782" s="2">
+        <v>31630</v>
       </c>
       <c r="F782" t="s">
         <v>196</v>
@@ -39226,13 +39182,13 @@
         <v>54</v>
       </c>
       <c r="C783" t="s">
-        <v>2226</v>
+        <v>2222</v>
       </c>
       <c r="D783" t="s">
-        <v>2227</v>
-      </c>
-      <c r="E783" t="s">
-        <v>2228</v>
+        <v>2223</v>
+      </c>
+      <c r="E783" s="2">
+        <v>68480</v>
       </c>
       <c r="F783" t="s">
         <v>196</v>
@@ -39272,8 +39228,8 @@
       <c r="D784" t="s">
         <v>2173</v>
       </c>
-      <c r="E784" t="s">
-        <v>511</v>
+      <c r="E784" s="2">
+        <v>75000</v>
       </c>
       <c r="F784" t="s">
         <v>18</v>
@@ -39313,8 +39269,8 @@
       <c r="D785" t="s">
         <v>2173</v>
       </c>
-      <c r="E785" t="s">
-        <v>2229</v>
+      <c r="E785" s="2">
+        <v>38217</v>
       </c>
       <c r="F785" t="s">
         <v>18</v>
@@ -39349,13 +39305,13 @@
         <v>132</v>
       </c>
       <c r="C786" t="s">
-        <v>2230</v>
+        <v>2224</v>
       </c>
       <c r="D786" t="s">
-        <v>2230</v>
-      </c>
-      <c r="E786" t="s">
-        <v>2231</v>
+        <v>2224</v>
+      </c>
+      <c r="E786" s="2">
+        <v>577978</v>
       </c>
       <c r="F786" t="s">
         <v>196</v>
@@ -39395,8 +39351,8 @@
       <c r="D787" t="s">
         <v>2191</v>
       </c>
-      <c r="E787" t="s">
-        <v>2192</v>
+      <c r="E787" s="2">
+        <v>50000</v>
       </c>
       <c r="F787" t="s">
         <v>18</v>
@@ -39431,13 +39387,13 @@
         <v>132</v>
       </c>
       <c r="C788" t="s">
-        <v>2232</v>
+        <v>2225</v>
       </c>
       <c r="D788" t="s">
-        <v>2232</v>
-      </c>
-      <c r="E788" t="s">
-        <v>2233</v>
+        <v>2225</v>
+      </c>
+      <c r="E788" s="2">
+        <v>55584</v>
       </c>
       <c r="F788" t="s">
         <v>196</v>
@@ -39477,8 +39433,8 @@
       <c r="D789" t="s">
         <v>1540</v>
       </c>
-      <c r="E789" t="s">
-        <v>2234</v>
+      <c r="E789" s="2">
+        <v>188148</v>
       </c>
       <c r="F789" t="s">
         <v>196</v>
@@ -39513,13 +39469,13 @@
         <v>180</v>
       </c>
       <c r="C790" t="s">
-        <v>2235</v>
+        <v>2226</v>
       </c>
       <c r="D790" t="s">
-        <v>2236</v>
-      </c>
-      <c r="E790" t="s">
-        <v>2237</v>
+        <v>2227</v>
+      </c>
+      <c r="E790" s="2">
+        <v>61595</v>
       </c>
       <c r="F790" t="s">
         <v>196</v>
@@ -39559,8 +39515,8 @@
       <c r="D791" t="s">
         <v>1540</v>
       </c>
-      <c r="E791" t="s">
-        <v>2238</v>
+      <c r="E791" s="2">
+        <v>98310</v>
       </c>
       <c r="F791" t="s">
         <v>196</v>
@@ -39595,13 +39551,13 @@
         <v>180</v>
       </c>
       <c r="C792" t="s">
-        <v>2239</v>
+        <v>2228</v>
       </c>
       <c r="D792" t="s">
-        <v>2240</v>
-      </c>
-      <c r="E792" t="s">
-        <v>2241</v>
+        <v>2229</v>
+      </c>
+      <c r="E792" s="2">
+        <v>35088</v>
       </c>
       <c r="F792" t="s">
         <v>196</v>
@@ -39641,8 +39597,8 @@
       <c r="D793" t="s">
         <v>2191</v>
       </c>
-      <c r="E793" t="s">
-        <v>2192</v>
+      <c r="E793" s="2">
+        <v>50000</v>
       </c>
       <c r="F793" t="s">
         <v>18</v>
@@ -39682,8 +39638,8 @@
       <c r="D794" t="s">
         <v>1540</v>
       </c>
-      <c r="E794" t="s">
-        <v>2242</v>
+      <c r="E794" s="2">
+        <v>486200</v>
       </c>
       <c r="F794" t="s">
         <v>196</v>
@@ -39721,10 +39677,10 @@
         <v>1581</v>
       </c>
       <c r="D795" t="s">
-        <v>2243</v>
-      </c>
-      <c r="E795" t="s">
-        <v>2244</v>
+        <v>2230</v>
+      </c>
+      <c r="E795" s="2">
+        <v>14164</v>
       </c>
       <c r="F795" t="s">
         <v>18</v>
@@ -39762,10 +39718,10 @@
         <v>1206</v>
       </c>
       <c r="D796" t="s">
-        <v>2245</v>
-      </c>
-      <c r="E796" t="s">
-        <v>2192</v>
+        <v>2231</v>
+      </c>
+      <c r="E796" s="1">
+        <v>50000</v>
       </c>
       <c r="F796" t="s">
         <v>18</v>
@@ -39800,13 +39756,13 @@
         <v>201</v>
       </c>
       <c r="C797" t="s">
-        <v>2246</v>
+        <v>2232</v>
       </c>
       <c r="D797" t="s">
-        <v>2247</v>
-      </c>
-      <c r="E797" t="s">
-        <v>2248</v>
+        <v>2233</v>
+      </c>
+      <c r="E797" s="2">
+        <v>147000</v>
       </c>
       <c r="F797" t="s">
         <v>196</v>
@@ -39841,13 +39797,13 @@
         <v>201</v>
       </c>
       <c r="C798" t="s">
-        <v>2246</v>
+        <v>2232</v>
       </c>
       <c r="D798" t="s">
-        <v>2249</v>
-      </c>
-      <c r="E798" t="s">
-        <v>2250</v>
+        <v>2234</v>
+      </c>
+      <c r="E798" s="2">
+        <v>550000</v>
       </c>
       <c r="F798" t="s">
         <v>196</v>
